--- a/results/05_transient_transcription_output/601/original_transcribed_data.xlsx
+++ b/results/05_transient_transcription_output/601/original_transcribed_data.xlsx
@@ -729,7 +729,7 @@
       <c r="C4" s="3" t="n"/>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -747,7 +747,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -771,14 +771,13 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="M4" s="3" t="n"/>
@@ -794,10 +793,14 @@
 </t>
         </is>
       </c>
-      <c r="P4" s="3" t="n"/>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">2150
 </t>
         </is>
       </c>
@@ -809,7 +812,7 @@
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -821,7 +824,7 @@
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
@@ -833,7 +836,7 @@
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>16</t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
@@ -844,10 +847,16 @@
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z4" s="3" t="n"/>
+          <t xml:space="preserve">55
+</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60
+</t>
+        </is>
+      </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>1</t>
@@ -861,7 +870,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n"/>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5082
+</t>
+        </is>
+      </c>
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="3" t="inlineStr">
         <is>
@@ -877,116 +891,121 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">155
+</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">146
+</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">61
+</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">928
+</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">224
+</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="T5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">615
+</t>
+        </is>
+      </c>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">104
+</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">183
+</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">270
+</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">157
-</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1146
-</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10920
-</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="Q5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">224
-</t>
-        </is>
-      </c>
-      <c r="R5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
-      <c r="S5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">167
-</t>
-        </is>
-      </c>
-      <c r="T5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">619
-</t>
-        </is>
-      </c>
-      <c r="U5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">104
-</t>
-        </is>
-      </c>
-      <c r="V5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">185
-</t>
-        </is>
-      </c>
-      <c r="W5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="X5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="Y5" s="3" t="n"/>
-      <c r="Z5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -1005,13 +1024,13 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5089
+          <t xml:space="preserve">529
 </t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">22441
 </t>
         </is>
       </c>
@@ -1023,7 +1042,8 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>75</t>
+          <t xml:space="preserve">125
+</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -1034,7 +1054,7 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -1046,102 +1066,97 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">140
+</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>418</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1318
+</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">920
+</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="n"/>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">212
+</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1436
+</t>
+        </is>
+      </c>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">135
+</t>
+        </is>
+      </c>
+      <c r="T6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">591
+</t>
+        </is>
+      </c>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">825
+</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">40
-</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>438</t>
-        </is>
-      </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1190
-</t>
-        </is>
-      </c>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0920
-</t>
-        </is>
-      </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1928
-</t>
-        </is>
-      </c>
-      <c r="P6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="Q6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11458
-</t>
-        </is>
-      </c>
-      <c r="R6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="S6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="T6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">591
-</t>
-        </is>
-      </c>
-      <c r="U6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="V6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
-      <c r="W6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="X6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
-      <c r="Y6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">870
-</t>
-        </is>
-      </c>
-      <c r="Z6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -1160,7 +1175,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5129
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -1172,18 +1187,19 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>165</t>
+          <t xml:space="preserve">125
+</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
@@ -1195,67 +1211,68 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
+          <t xml:space="preserve">234
 </t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1136
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">9837
 </t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">7181
 </t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1206
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1125
+          <t xml:space="preserve">425
 </t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">1776
 </t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>841</t>
+          <t xml:space="preserve">174
+</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
@@ -1266,7 +1283,7 @@
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">978
 </t>
         </is>
       </c>
@@ -1278,25 +1295,25 @@
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
@@ -1315,7 +1332,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2298
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
@@ -1333,72 +1350,67 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">18
 </t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>56</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
-</t>
-        </is>
-      </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1959
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">950
+</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="n"/>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11205
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
@@ -1410,49 +1422,49 @@
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">760
+</t>
+        </is>
+      </c>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">58
+</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">171
+</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">160
 </t>
         </is>
       </c>
-      <c r="U8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">82
-</t>
-        </is>
-      </c>
-      <c r="V8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">171
-</t>
-        </is>
-      </c>
-      <c r="W8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">808
+          <t xml:space="preserve">900
 </t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -1471,75 +1483,80 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4450</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>185</t>
+          <t xml:space="preserve">11835
+</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6156
+          <t xml:space="preserve">676
 </t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="n"/>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>091</t>
+        </is>
+      </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>634</t>
+          <t xml:space="preserve">631
+</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>2061</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>2644</t>
+          <t xml:space="preserve">164
+</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">511
+          <t xml:space="preserve">17179190
+1
 </t>
         </is>
       </c>
       <c r="L9" s="3" t="n"/>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">689
+          <t xml:space="preserve">659
 </t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">459
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1140
+          <t xml:space="preserve">1738
 </t>
         </is>
       </c>
@@ -1550,46 +1567,46 @@
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>661</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>76</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t>53010</t>
+          <t xml:space="preserve">30
+</t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1940
-</t>
+          <t>401</t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">828
 </t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">451
 </t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
@@ -1608,7 +1625,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>4450</t>
+          <t>1948</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -1625,35 +1642,40 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2
+</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">33
+</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">102
 </t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">33
-</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="n"/>
       <c r="L10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">147
@@ -1668,14 +1690,13 @@
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>8801</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
@@ -1686,31 +1707,31 @@
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">76
 </t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">625
+          <t xml:space="preserve">628
 </t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -1728,19 +1749,19 @@
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">897
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10884
+          <t xml:space="preserve">830
 </t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -1759,12 +1780,13 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>1548</t>
+          <t xml:space="preserve">2989
+</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -1782,12 +1804,13 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>331</t>
+          <t xml:space="preserve">88
+</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>1481</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -1798,37 +1821,38 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">087
 </t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">14686
 </t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>830</t>
+          <t xml:space="preserve">20
+</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
@@ -1839,62 +1863,60 @@
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">22
+198
 </t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">399
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1638
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
-</t>
+          <t>940</t>
         </is>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AA11" s="3" t="inlineStr">
@@ -1912,19 +1934,19 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2295
+          <t xml:space="preserve">2989
 </t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1224
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -1936,73 +1958,73 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1091
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">10
 </t>
         </is>
       </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1139
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">945
 </t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1171
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
@@ -2014,13 +2036,13 @@
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">745
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
@@ -2038,18 +2060,20 @@
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t>940</t>
+          <t xml:space="preserve">850
+</t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t>401</t>
+          <t xml:space="preserve">28
+</t>
         </is>
       </c>
       <c r="AA12" s="3" t="inlineStr">
@@ -2067,13 +2091,13 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293220
+          <t xml:space="preserve">324
 </t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">636
 </t>
         </is>
       </c>
@@ -2091,7 +2115,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">498
 </t>
         </is>
       </c>
@@ -2103,13 +2127,13 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -2128,78 +2152,74 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
-        </is>
-      </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>9464</t>
-        </is>
-      </c>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="n"/>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1582
+</t>
+        </is>
+      </c>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1685
+</t>
+        </is>
+      </c>
+      <c r="T13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">167
+</t>
+        </is>
+      </c>
+      <c r="W13" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">158
 </t>
         </is>
       </c>
-      <c r="R13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="S13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="T13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">018
-</t>
-        </is>
-      </c>
-      <c r="U13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="V13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">167
-</t>
-        </is>
-      </c>
-      <c r="W13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1158
-</t>
-        </is>
-      </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
+          <t xml:space="preserve">928
 </t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -2216,12 +2236,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3240
-</t>
-        </is>
-      </c>
+      <c r="C14" s="3" t="n"/>
       <c r="D14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">218
@@ -2230,7 +2245,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -2242,19 +2257,19 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -2264,7 +2279,12 @@
 </t>
         </is>
       </c>
-      <c r="K14" s="3" t="n"/>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">53
+</t>
+        </is>
+      </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">144
@@ -2279,20 +2299,25 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1583
-</t>
-        </is>
-      </c>
-      <c r="O14" s="3" t="n"/>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">66
+</t>
+        </is>
+      </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1215
+          <t xml:space="preserve">1413
 </t>
         </is>
       </c>
@@ -2304,19 +2329,19 @@
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1181
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1719
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1712
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -2334,19 +2359,19 @@
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -2365,37 +2390,41 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3079
+          <t xml:space="preserve">14755
 </t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="n"/>
+          <t>451</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1126
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">1121
 </t>
         </is>
       </c>
@@ -2407,37 +2436,26 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1142
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
-</t>
-        </is>
-      </c>
-      <c r="N15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">155
-</t>
-        </is>
-      </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">968
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="n"/>
+      <c r="O15" s="3" t="n"/>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>16</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -2454,13 +2472,13 @@
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1169
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">730
+          <t xml:space="preserve">3730
 </t>
         </is>
       </c>
@@ -2484,19 +2502,19 @@
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8855
+          <t xml:space="preserve">3410
 </t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -2515,19 +2533,19 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14259
+          <t xml:space="preserve">1416
 </t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>684</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -2537,13 +2555,13 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11074
+          <t xml:space="preserve">474
 </t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>6441</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
@@ -2553,83 +2571,93 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>649</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="n"/>
       <c r="L16" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">732
 </t>
         </is>
       </c>
-      <c r="M16" s="3" t="n"/>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">694
+</t>
+        </is>
+      </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="O16" s="3" t="n"/>
+          <t xml:space="preserve">5117
+18
+</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">60
+</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>234</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t>881</t>
+          <t xml:space="preserve">880
+</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t>324</t>
+          <t xml:space="preserve">39945
+</t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>448</t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1845
+          <t xml:space="preserve">843
 </t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>256</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>561</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">482
 </t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
@@ -2648,25 +2676,25 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
+          <t xml:space="preserve">1343
 </t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
+          <t xml:space="preserve">1481
 </t>
         </is>
       </c>
@@ -2678,55 +2706,54 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">79
+</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>004</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46
+</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">139
+</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="n"/>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">12
 </t>
         </is>
       </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="n"/>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">746
-</t>
-        </is>
-      </c>
-      <c r="M17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">139
-</t>
-        </is>
-      </c>
-      <c r="N17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="P17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
@@ -2744,41 +2771,43 @@
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">789
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1169
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>867</t>
+          <t xml:space="preserve">172
+</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t>502</t>
+          <t xml:space="preserve">91
+</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -2797,19 +2826,18 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2250
+          <t xml:space="preserve">4285
 </t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1249
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
@@ -2821,19 +2849,30 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>184</t>
+          <t xml:space="preserve">14
+</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>199</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="n"/>
-      <c r="J18" s="3" t="n"/>
+          <t xml:space="preserve">109
+</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>00</t>
+          <t xml:space="preserve">187
+</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
@@ -2844,35 +2883,38 @@
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>911</t>
+          <t xml:space="preserve">920
+</t>
         </is>
       </c>
       <c r="P18" s="3" t="n"/>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>35</t>
+          <t xml:space="preserve">218
+</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t xml:space="preserve">178
+</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>181</t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
@@ -2893,26 +2935,23 @@
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">901
-</t>
+          <t>810</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>4104</t>
         </is>
       </c>
       <c r="AA18" s="3" t="inlineStr">
@@ -2930,7 +2969,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4285
+          <t xml:space="preserve">4406
 </t>
         </is>
       </c>
@@ -2948,19 +2987,19 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">1952
 </t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1121
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
@@ -2972,13 +3011,13 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
@@ -2990,25 +3029,21 @@
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1542
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">920
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">112
+7
+</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="n"/>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">514
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -3026,48 +3061,50 @@
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">540
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1144
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1672
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t>81</t>
+          <t xml:space="preserve">8105
+</t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t>401</t>
+          <t xml:space="preserve">44
+</t>
         </is>
       </c>
       <c r="AA19" s="3" t="inlineStr">
@@ -3085,31 +3122,31 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4406
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">769
 </t>
         </is>
       </c>
@@ -3120,15 +3157,10 @@
         </is>
       </c>
       <c r="I20" s="3" t="n"/>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
+      <c r="J20" s="3" t="n"/>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
@@ -3140,55 +3172,57 @@
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1151
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">112
+7
 </t>
         </is>
       </c>
       <c r="O20" s="3" t="n"/>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t>125</t>
+          <t xml:space="preserve">185
+</t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">768
+          <t xml:space="preserve">468
 </t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
@@ -3200,19 +3234,19 @@
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -3231,25 +3265,25 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1531
+          <t xml:space="preserve">24617
 </t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">2419
 </t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
@@ -3261,11 +3295,16 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="n"/>
+          <t xml:space="preserve">141
+</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">115
@@ -3274,7 +3313,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
@@ -3292,20 +3331,25 @@
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1970
-</t>
-        </is>
-      </c>
-      <c r="O21" s="3" t="n"/>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">2414
 </t>
         </is>
       </c>
@@ -3323,13 +3367,13 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">748
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
@@ -3341,24 +3385,25 @@
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t xml:space="preserve">170
+</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -3377,19 +3422,19 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2617
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">2066
 </t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
@@ -3401,92 +3446,86 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">146
+</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="n"/>
+      <c r="O22" s="3" t="n"/>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70
+</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">264
+</t>
+        </is>
+      </c>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="S22" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">18
 </t>
         </is>
       </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">85
-</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30
-</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1125
-</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">146
-</t>
-        </is>
-      </c>
-      <c r="N22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">918
-</t>
-        </is>
-      </c>
-      <c r="P22" s="3" t="n"/>
-      <c r="Q22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="R22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
-      <c r="S22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1178
-</t>
-        </is>
-      </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">740
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">562
 </t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -3496,21 +3535,16 @@
 </t>
         </is>
       </c>
-      <c r="X22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
+      <c r="X22" s="3" t="n"/>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">945
+          <t xml:space="preserve">455
 </t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -3529,7 +3563,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1233
+          <t xml:space="preserve">1477
 </t>
         </is>
       </c>
@@ -3539,11 +3573,14 @@
 </t>
         </is>
       </c>
-      <c r="E23" s="3" t="n"/>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -3552,23 +3589,15 @@
 </t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>6170</t>
-        </is>
-      </c>
+      <c r="H23" s="3" t="n"/>
       <c r="I23" s="3" t="n"/>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t>33211</t>
-        </is>
-      </c>
+          <t xml:space="preserve">73
+</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="n"/>
       <c r="L23" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">762
@@ -3578,25 +3607,25 @@
       <c r="M23" s="3" t="n"/>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1090
+          <t xml:space="preserve">1798
 </t>
         </is>
       </c>
@@ -3614,7 +3643,7 @@
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t>4141</t>
+          <t>419</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
@@ -3625,30 +3654,29 @@
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t>942</t>
+          <t>442</t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>83</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>72</t>
+          <t xml:space="preserve">23
+</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4995
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>1581</t>
         </is>
       </c>
       <c r="AA23" s="3" t="inlineStr">
@@ -3666,8 +3694,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14779
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -3678,7 +3705,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -3690,15 +3717,11 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="n"/>
       <c r="I24" s="3" t="inlineStr">
         <is>
           <t>15</t>
@@ -3710,15 +3733,10 @@
 </t>
         </is>
       </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
+      <c r="K24" s="3" t="n"/>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -3728,27 +3746,18 @@
 </t>
         </is>
       </c>
-      <c r="N24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
+      <c r="N24" s="3" t="n"/>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">924
-</t>
-        </is>
-      </c>
-      <c r="P24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">16
+111
+</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="n"/>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -3760,13 +3769,13 @@
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">1281
 </t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">896
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
@@ -3784,25 +3793,26 @@
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">1111
 </t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">871
+          <t xml:space="preserve">940
 </t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t>1581</t>
+          <t xml:space="preserve">28
+</t>
         </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -3820,84 +3830,80 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>46</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>97</t>
+          <t xml:space="preserve">226
+</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>961</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>146</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>901</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="n"/>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
-</t>
+          <t>451</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1142
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">915
-</t>
-        </is>
-      </c>
-      <c r="P25" s="3" t="n"/>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="n"/>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>11454</t>
         </is>
       </c>
       <c r="R25" s="3" t="n"/>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t>116</t>
+          <t xml:space="preserve">176
+</t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
@@ -3919,25 +3925,25 @@
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
+          <t xml:space="preserve">885
 </t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -3956,13 +3962,13 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8904
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1225
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -3974,19 +3980,19 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">1891
 </t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>138</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
@@ -4003,13 +4009,14 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">81
+1198
 </t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1846
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
@@ -4021,19 +4028,19 @@
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">406
 </t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -4045,7 +4052,7 @@
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1175
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
@@ -4057,7 +4064,7 @@
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17130
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
@@ -4069,7 +4076,7 @@
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -4080,19 +4087,19 @@
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
+          <t xml:space="preserve">918
 </t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -4111,13 +4118,13 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3260
+          <t xml:space="preserve">535
 </t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
@@ -4135,7 +4142,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
@@ -4154,44 +4161,49 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
-        </is>
-      </c>
-      <c r="L27" s="3" t="n"/>
+          <t xml:space="preserve">154
+</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">154
+</t>
+        </is>
+      </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1950
+          <t xml:space="preserve">950
 </t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2108
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -4203,13 +4215,13 @@
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">780
+          <t xml:space="preserve">70
 </t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
@@ -4227,19 +4239,19 @@
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
+          <t xml:space="preserve">838
 </t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -4258,31 +4270,31 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2818
+          <t xml:space="preserve">2898
 </t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">418
 </t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1538
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
@@ -4294,19 +4306,20 @@
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">9799791979277
+2 8
 </t>
         </is>
       </c>
@@ -4318,13 +4331,13 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1142
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -4336,13 +4349,13 @@
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">2108
 </t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
@@ -4354,13 +4367,13 @@
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1768
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">728
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -4384,19 +4397,19 @@
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">1851
 </t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8308
+          <t xml:space="preserve">850
 </t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -4415,13 +4428,13 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23059
+          <t xml:space="preserve">1999
 </t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11219
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
@@ -4433,7 +4446,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -4451,74 +4464,69 @@
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1849
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
+          <t>7144</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="n"/>
+      <c r="Q29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">217
+</t>
+        </is>
+      </c>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1121
+</t>
+        </is>
+      </c>
+      <c r="T29" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">18
 </t>
         </is>
       </c>
-      <c r="O29" s="3" t="n"/>
-      <c r="P29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
-      </c>
-      <c r="Q29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">217
-</t>
-        </is>
-      </c>
-      <c r="R29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="S29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1821
-</t>
-        </is>
-      </c>
-      <c r="T29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
@@ -4534,16 +4542,10 @@
 </t>
         </is>
       </c>
-      <c r="X29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">185
-</t>
-        </is>
-      </c>
+      <c r="X29" s="3" t="n"/>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
-</t>
+          <t>1474</t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
@@ -4567,7 +4569,8 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2898
+          <t xml:space="preserve">1921
+188181
 </t>
         </is>
       </c>
@@ -4576,62 +4579,67 @@
           <t>7162</t>
         </is>
       </c>
-      <c r="E30" s="3" t="n"/>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">686
+</t>
+        </is>
+      </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">906
+          <t xml:space="preserve">9661
 </t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>45700</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">666
-</t>
+          <t>66611</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115656
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="J30" s="3" t="n"/>
-      <c r="K30" s="3" t="inlineStr">
-        <is>
-          <t>3501</t>
-        </is>
-      </c>
-      <c r="L30" s="3" t="n"/>
+      <c r="K30" s="3" t="n"/>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7197
+</t>
+        </is>
+      </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>773</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">717
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>201</t>
+          <t xml:space="preserve">10
+</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10562
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
@@ -4640,30 +4648,53 @@
           <t>8244</t>
         </is>
       </c>
-      <c r="S30" s="3" t="n"/>
-      <c r="T30" s="3" t="n"/>
+      <c r="S30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">368883
+101
+</t>
+        </is>
+      </c>
+      <c r="T30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9242175
+993 6
+</t>
+        </is>
+      </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>2461</t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="W30" s="3" t="n"/>
-      <c r="X30" s="3" t="n"/>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="W30" s="3" t="inlineStr">
+        <is>
+          <t>841</t>
+        </is>
+      </c>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">777
+1
+17
+</t>
+        </is>
+      </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t>144</t>
+          <t xml:space="preserve">83
+</t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>751</t>
         </is>
       </c>
       <c r="AA30" s="3" t="inlineStr">
@@ -4681,13 +4712,13 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -4727,11 +4758,15 @@
 </t>
         </is>
       </c>
-      <c r="K31" s="3" t="n"/>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7
+</t>
+        </is>
+      </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
@@ -4742,13 +4777,12 @@
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11705
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">941
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
@@ -4760,7 +4794,7 @@
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -4772,16 +4806,11 @@
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="T31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">723
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">7900
+</t>
+        </is>
+      </c>
+      <c r="T31" s="3" t="n"/>
       <c r="U31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">69
@@ -4790,31 +4819,27 @@
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
-      <c r="X31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">177
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">62
+</t>
+        </is>
+      </c>
+      <c r="X31" s="3" t="n"/>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">883
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t>75</t>
+          <t xml:space="preserve">24
+</t>
         </is>
       </c>
       <c r="AA31" s="3" t="inlineStr">
@@ -4832,13 +4857,13 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3220
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">1215
 </t>
         </is>
       </c>
@@ -4850,64 +4875,70 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>831</t>
+          <t>131</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">11
+</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">7
 </t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="N32" s="3" t="n"/>
+          <t>4451</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">78
+</t>
+        </is>
+      </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1170
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
@@ -4919,20 +4950,19 @@
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">7900
 </t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">515
 </t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
@@ -4949,14 +4979,20 @@
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="Y32" s="3" t="n"/>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="Y32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
+710
+</t>
+        </is>
+      </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
@@ -4975,13 +5011,13 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2355
+          <t xml:space="preserve">4828
 </t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -4993,25 +5029,25 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1882
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8786
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
@@ -5023,13 +5059,13 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1157
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1137
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
@@ -5041,79 +5077,79 @@
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">78
+</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30
+</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="T33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">515
+</t>
+        </is>
+      </c>
+      <c r="U33" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">18
 </t>
         </is>
       </c>
-      <c r="O33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">930
-</t>
-        </is>
-      </c>
-      <c r="P33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">110
-</t>
-        </is>
-      </c>
-      <c r="Q33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1248
-</t>
-        </is>
-      </c>
-      <c r="R33" s="3" t="inlineStr">
+      <c r="V33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="W33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">154
+</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">168
 </t>
         </is>
       </c>
-      <c r="S33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">152
-</t>
-        </is>
-      </c>
-      <c r="T33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">515
-</t>
-        </is>
-      </c>
-      <c r="U33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11144
-</t>
-        </is>
-      </c>
-      <c r="V33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="W33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">154
-</t>
-        </is>
-      </c>
-      <c r="X33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">718
+          <t xml:space="preserve">808
 </t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
@@ -5138,13 +5174,14 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">4241
 </t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>06</t>
+          <t xml:space="preserve">115
+</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
@@ -5155,13 +5192,14 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">112179 1
+</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
@@ -5178,7 +5216,7 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
@@ -5190,61 +5228,62 @@
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4116
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">177
+1
+</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">920
+</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="Q34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">159
+</t>
+        </is>
+      </c>
+      <c r="R34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="S34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">152
+</t>
+        </is>
+      </c>
+      <c r="T34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7144
+</t>
+        </is>
+      </c>
+      <c r="U34" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">18
 </t>
         </is>
       </c>
-      <c r="O34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">920
-</t>
-        </is>
-      </c>
-      <c r="P34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="Q34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">239
-</t>
-        </is>
-      </c>
-      <c r="R34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">177
-</t>
-        </is>
-      </c>
-      <c r="S34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1168
-</t>
-        </is>
-      </c>
-      <c r="T34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">568
-</t>
-        </is>
-      </c>
-      <c r="U34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -5256,13 +5295,14 @@
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1167
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">14
+247
 </t>
         </is>
       </c>
@@ -5287,36 +5327,36 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4828
+          <t xml:space="preserve">4928
 </t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112150
+          <t xml:space="preserve">1501
 </t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>436</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">1937
 </t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1894
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -5334,7 +5374,7 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
@@ -5346,19 +5386,20 @@
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1155
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">910
 </t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">14181
+60
 </t>
         </is>
       </c>
@@ -5370,7 +5411,7 @@
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">845
+          <t xml:space="preserve">1457
 </t>
         </is>
       </c>
@@ -5382,13 +5423,13 @@
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6009
+          <t xml:space="preserve">568
 </t>
         </is>
       </c>
@@ -5400,25 +5441,25 @@
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1207
+          <t xml:space="preserve">12067
 </t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">1851
 </t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">758
+          <t xml:space="preserve">798
 </t>
         </is>
       </c>
@@ -5449,25 +5490,25 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">1242
 </t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1539
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1981
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1103
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
@@ -5479,13 +5520,13 @@
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">2235
 </t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -5503,19 +5544,14 @@
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="N36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">115
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">156
+</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="n"/>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
+          <t xml:space="preserve">9180
 </t>
         </is>
       </c>
@@ -5527,7 +5563,7 @@
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2141
+          <t xml:space="preserve">1441
 </t>
         </is>
       </c>
@@ -5539,19 +5575,19 @@
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">1828
 </t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">551
+          <t xml:space="preserve">608
 </t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -5569,7 +5605,7 @@
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">1661
 </t>
         </is>
       </c>
@@ -5581,7 +5617,7 @@
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
@@ -5600,24 +5636,22 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>24923</t>
+          <t>9280</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>1194</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">658
-</t>
+          <t>768</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">986
-</t>
+          <t>926</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
@@ -5628,47 +5662,38 @@
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">619
+          <t xml:space="preserve">6139
 </t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11106
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1218
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1757
-</t>
-        </is>
-      </c>
-      <c r="M37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">702
-</t>
-        </is>
-      </c>
-      <c r="N37" s="3" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
+          <t xml:space="preserve">757
+</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="n"/>
+      <c r="N37" s="3" t="n"/>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1490
+          <t xml:space="preserve">44980
 </t>
         </is>
       </c>
@@ -5680,54 +5705,57 @@
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">871
 </t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t>4344</t>
+          <t xml:space="preserve">581
+</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2348
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>3771</t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8098
+          <t xml:space="preserve">8048
 </t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">858
-</t>
-        </is>
-      </c>
-      <c r="Y37" s="3" t="n"/>
+          <t>852</t>
+        </is>
+      </c>
+      <c r="Y37" s="3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -5746,7 +5774,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4386
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
@@ -5764,25 +5792,25 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -5792,72 +5820,66 @@
 </t>
         </is>
       </c>
-      <c r="K38" s="3" t="inlineStr">
+      <c r="K38" s="3" t="n"/>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">141
+</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">899
+</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">61718682
+68
+8987
+</t>
+        </is>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4 8
+21 0
+</t>
+        </is>
+      </c>
+      <c r="Q38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27
+</t>
+        </is>
+      </c>
+      <c r="R38" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
-      <c r="L38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">151
-</t>
-        </is>
-      </c>
-      <c r="M38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">140
-</t>
-        </is>
-      </c>
-      <c r="N38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="O38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
-      <c r="P38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="Q38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">227
-</t>
-        </is>
-      </c>
-      <c r="R38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
+14
 </t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">848
 </t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
-        </is>
-      </c>
-      <c r="U38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">110
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">314
+</t>
+        </is>
+      </c>
+      <c r="U38" s="3" t="n"/>
       <c r="V38" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">182
@@ -5872,7 +5894,7 @@
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1731
+          <t xml:space="preserve">1721
 </t>
         </is>
       </c>
@@ -5903,19 +5925,19 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3955
+          <t xml:space="preserve">583
 </t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -5926,7 +5948,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>71</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
@@ -5937,13 +5959,12 @@
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>715</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
@@ -5955,18 +5976,19 @@
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>466</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>501</t>
+          <t>50</t>
         </is>
       </c>
       <c r="N39" s="3" t="n"/>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">898
+          <t xml:space="preserve">10
+8917
 </t>
         </is>
       </c>
@@ -5977,42 +5999,43 @@
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">1536
 </t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t>77</t>
+          <t xml:space="preserve">116
+</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">520
+          <t xml:space="preserve">647
 </t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11911
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
@@ -6024,13 +6047,13 @@
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">714
 </t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>641</t>
         </is>
       </c>
       <c r="AA39" s="3" t="inlineStr">
@@ -6048,12 +6071,13 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>54521</t>
+          <t xml:space="preserve">5451
+</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
@@ -6077,25 +6101,25 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1115
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">23530
 </t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">47
 </t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -6107,46 +6131,47 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1136
+          <t xml:space="preserve">13536
 </t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">889
+</t>
+        </is>
+      </c>
+      <c r="O40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+6
+</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="Q40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
+      <c r="R40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="S40" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">11
 </t>
         </is>
       </c>
-      <c r="O40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="P40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="Q40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="R40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="S40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">585
@@ -6155,7 +6180,7 @@
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -6167,19 +6192,19 @@
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">1280
 </t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">720
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -6222,31 +6247,31 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
+          <t xml:space="preserve">77
 </t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1140
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -6264,19 +6289,19 @@
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1389
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">889
 </t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">889
+          <t xml:space="preserve">87701
 </t>
         </is>
       </c>
@@ -6288,19 +6313,19 @@
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">2382
 </t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1808
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -6318,13 +6343,13 @@
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">1960
 </t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1170
+          <t xml:space="preserve">16585
 </t>
         </is>
       </c>
@@ -6367,13 +6392,14 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1224
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
+          <t xml:space="preserve">191
+181
 </t>
         </is>
       </c>
@@ -6385,13 +6411,13 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
+          <t xml:space="preserve">1211
 </t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1137
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
@@ -6403,38 +6429,44 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6146
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">01
 </t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16211
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1159
-</t>
-        </is>
-      </c>
-      <c r="N42" s="3" t="n"/>
+          <t xml:space="preserve">151
+</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2924
+991
+</t>
+        </is>
+      </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 111
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -6446,7 +6478,7 @@
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1671
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
@@ -6458,43 +6490,43 @@
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">605
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1898
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">818
 </t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">537
 </t>
         </is>
       </c>
@@ -6513,144 +6545,145 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">53109
+          <t xml:space="preserve">570
 </t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2392
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1131
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">18070
+</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42
+</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2008
+</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">134
+</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3170
+</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9271
+</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1128
+</t>
+        </is>
+      </c>
+      <c r="R43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">115
+</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">156
+</t>
+        </is>
+      </c>
+      <c r="T43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">588
+</t>
+        </is>
+      </c>
+      <c r="U43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="V43" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">181
 </t>
         </is>
       </c>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">101
-</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1114
-</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42
-</t>
-        </is>
-      </c>
-      <c r="K43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L43" s="3" t="inlineStr">
+      <c r="W43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">151
+</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">148
 </t>
         </is>
       </c>
-      <c r="M43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1184
-</t>
-        </is>
-      </c>
-      <c r="N43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1910
-</t>
-        </is>
-      </c>
-      <c r="O43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">810
-</t>
-        </is>
-      </c>
-      <c r="P43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
-      <c r="Q43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1222
-</t>
-        </is>
-      </c>
-      <c r="R43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
-      <c r="S43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="T43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">580
-</t>
-        </is>
-      </c>
-      <c r="U43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="V43" s="3" t="inlineStr">
-        <is>
-          <t>411</t>
-        </is>
-      </c>
-      <c r="W43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1150
-</t>
-        </is>
-      </c>
-      <c r="X43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">780
 </t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
@@ -6669,145 +6702,143 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8571
+          <t xml:space="preserve">51
 </t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
+          <t xml:space="preserve">634
 </t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>1825</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">610
+</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50
+</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5409
+</t>
+        </is>
+      </c>
+      <c r="O44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+1272971
+</t>
+        </is>
+      </c>
+      <c r="P44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4
+</t>
+        </is>
+      </c>
+      <c r="Q44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
+      <c r="R44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">167
+</t>
+        </is>
+      </c>
+      <c r="S44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="T44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">595
+</t>
+        </is>
+      </c>
+      <c r="U44" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">108
 </t>
         </is>
       </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1114
-</t>
-        </is>
-      </c>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">146
-</t>
-        </is>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">50
-</t>
-        </is>
-      </c>
-      <c r="K44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1836
-</t>
-        </is>
-      </c>
-      <c r="M44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1896
-</t>
-        </is>
-      </c>
-      <c r="N44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5408
-</t>
-        </is>
-      </c>
-      <c r="O44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">918
-</t>
-        </is>
-      </c>
-      <c r="P44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="Q44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="R44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">167
-</t>
-        </is>
-      </c>
-      <c r="S44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">129
-</t>
-        </is>
-      </c>
-      <c r="T44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1595
-</t>
-        </is>
-      </c>
-      <c r="U44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1108
-</t>
-        </is>
-      </c>
       <c r="V44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">1118
 </t>
         </is>
       </c>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="X44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">4668
 </t>
         </is>
       </c>
       <c r="Y44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7240
-</t>
+          <t>664</t>
         </is>
       </c>
       <c r="Z44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">881
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
@@ -6826,89 +6857,86 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2283
+          <t xml:space="preserve">2830
 </t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">77
+</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">133
+</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">610
+</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">708
+</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">152
+</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2152
+</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">11
 </t>
         </is>
       </c>
-      <c r="E45" s="3" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="F45" s="3" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="G45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6210
-</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">708
-</t>
-        </is>
-      </c>
-      <c r="I45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">252
-</t>
-        </is>
-      </c>
-      <c r="K45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">01
-</t>
-        </is>
-      </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8985
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8511
+          <t xml:space="preserve">8871
 </t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="O45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5409
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="n"/>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
@@ -6919,19 +6947,19 @@
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9756
+          <t xml:space="preserve">9792
 </t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35611
+          <t xml:space="preserve">3511
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">690
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -6943,22 +6971,28 @@
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">958
+          <t xml:space="preserve">6
 </t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
+          <t xml:space="preserve">92926
 </t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t>1668</t>
-        </is>
-      </c>
-      <c r="Z45" s="3" t="n"/>
+          <t xml:space="preserve">78
+</t>
+        </is>
+      </c>
+      <c r="Z45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">287
+</t>
+        </is>
+      </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -6980,25 +7014,21 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">133
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">818
+4236
+</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="n"/>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1103
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
@@ -7020,28 +7050,27 @@
 </t>
         </is>
       </c>
-      <c r="K46" s="3" t="n"/>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="M46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="n"/>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">901
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
@@ -7059,7 +7088,7 @@
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1718
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -7071,25 +7100,20 @@
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">585
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
-        </is>
-      </c>
-      <c r="V46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="V46" s="3" t="n"/>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -7101,7 +7125,7 @@
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/601/original_transcribed_data.xlsx
+++ b/results/05_transient_transcription_output/601/original_transcribed_data.xlsx
@@ -728,7 +728,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5823
+          <t xml:space="preserve">5829
 </t>
         </is>
       </c>
@@ -744,7 +744,12 @@
 </t>
         </is>
       </c>
-      <c r="F4" s="3" t="n"/>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">115
@@ -753,25 +758,54 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="n"/>
-      <c r="J4" s="3" t="n"/>
-      <c r="K4" s="3" t="n"/>
+          <t xml:space="preserve">131
+</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>451</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="n"/>
-      <c r="N4" s="3" t="n"/>
-      <c r="O4" s="3" t="n"/>
+          <t xml:space="preserve">117
+</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">131
+</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">870
+</t>
+        </is>
+      </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">22
+</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -792,12 +826,26 @@
 </t>
         </is>
       </c>
-      <c r="T4" s="3" t="n"/>
-      <c r="U4" s="3" t="n"/>
-      <c r="V4" s="3" t="n"/>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1520
+</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11207
+</t>
+        </is>
+      </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -819,27 +867,37 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3888
-</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="n"/>
+          <t xml:space="preserve">2889
+</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1108
+</t>
+        </is>
+      </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">872
-</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="n"/>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
+          <t xml:space="preserve">1123
 </t>
         </is>
       </c>
@@ -851,26 +909,61 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="n"/>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">127
+</t>
+        </is>
+      </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="n"/>
-      <c r="N5" s="3" t="n"/>
-      <c r="O5" s="3" t="n"/>
-      <c r="P5" s="3" t="n"/>
-      <c r="Q5" s="3" t="n"/>
-      <c r="R5" s="3" t="n"/>
+          <t xml:space="preserve">135
+</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">161
+</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">920
+</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">224
+</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">1167
 </t>
         </is>
       </c>
@@ -894,7 +987,7 @@
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
@@ -904,7 +997,12 @@
 </t>
         </is>
       </c>
-      <c r="Y5" s="3" t="n"/>
+      <c r="Y5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">755
+</t>
+        </is>
+      </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">60
@@ -926,45 +1024,106 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25089
-</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="n"/>
-      <c r="E6" s="3" t="n"/>
+          <t xml:space="preserve">5089
+</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">241
+</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>136</t>
+          <t xml:space="preserve">1180
+</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="n"/>
-      <c r="I6" s="3" t="n"/>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
-</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="n"/>
-      <c r="L6" s="3" t="n"/>
+          <t xml:space="preserve">48
+</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1138
+</t>
+        </is>
+      </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">130
 </t>
         </is>
       </c>
-      <c r="N6" s="3" t="n"/>
-      <c r="O6" s="3" t="n"/>
-      <c r="P6" s="3" t="n"/>
-      <c r="Q6" s="3" t="n"/>
-      <c r="R6" s="3" t="n"/>
-      <c r="S6" s="3" t="n"/>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">920
+</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">256
+</t>
+        </is>
+      </c>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">619
@@ -979,24 +1138,34 @@
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">1168
 </t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="Y6" s="3" t="n"/>
-      <c r="Z6" s="3" t="n"/>
+          <t xml:space="preserve">1181
+</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">870
+</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
           <t>3</t>
@@ -1016,7 +1185,12 @@
 </t>
         </is>
       </c>
-      <c r="D7" s="3" t="n"/>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">239
+</t>
+        </is>
+      </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">132
@@ -1025,48 +1199,80 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">11898
+</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">107
+</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">120
+</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">34
+</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">880
+</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">143
+</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1236
+</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">188
 </t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">107
-</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="n"/>
-      <c r="I7" s="3" t="n"/>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">39
-</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="n"/>
-      <c r="L7" s="3" t="n"/>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="N7" s="3" t="n"/>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>410</t>
+          <t xml:space="preserve">5930
+</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="Q7" s="3" t="n"/>
-      <c r="R7" s="3" t="n"/>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
@@ -1078,20 +1284,40 @@
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11918
-</t>
-        </is>
-      </c>
-      <c r="V7" s="3" t="n"/>
+          <t xml:space="preserve">1118
+</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="X7" s="3" t="n"/>
-      <c r="Y7" s="3" t="n"/>
-      <c r="Z7" s="3" t="n"/>
+          <t xml:space="preserve">1166
+</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">177
+</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">821
+</t>
+        </is>
+      </c>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01
+</t>
+        </is>
+      </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
           <t>4</t>
@@ -1111,10 +1337,15 @@
 </t>
         </is>
       </c>
-      <c r="D8" s="3" t="n"/>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">419
+</t>
+        </is>
+      </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
@@ -1130,7 +1361,12 @@
 </t>
         </is>
       </c>
-      <c r="H8" s="3" t="n"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">129
+</t>
+        </is>
+      </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">18
@@ -1145,7 +1381,8 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>77</t>
+          <t xml:space="preserve">272
+</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -1160,26 +1397,51 @@
 </t>
         </is>
       </c>
-      <c r="N8" s="3" t="n"/>
-      <c r="O8" s="3" t="n"/>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">08
 </t>
         </is>
       </c>
-      <c r="Q8" s="3" t="n"/>
-      <c r="R8" s="3" t="n"/>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">205
+</t>
+        </is>
+      </c>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="T8" s="3" t="n"/>
+          <t xml:space="preserve">1181
+</t>
+        </is>
+      </c>
+      <c r="T8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">760
+</t>
+        </is>
+      </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -1189,7 +1451,12 @@
 </t>
         </is>
       </c>
-      <c r="W8" s="3" t="n"/>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
       <c r="X8" s="3" t="n"/>
       <c r="Y8" s="3" t="n"/>
       <c r="Z8" s="3" t="n"/>
@@ -1220,7 +1487,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">676
+          <t xml:space="preserve">616
 </t>
         </is>
       </c>
@@ -1232,37 +1499,55 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2694</t>
+          <t xml:space="preserve">8815
+</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>634</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="n"/>
+          <t xml:space="preserve">651
+</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">105
+</t>
+        </is>
+      </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1164
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">511
-</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="n"/>
-      <c r="M9" s="3" t="n"/>
+          <t xml:space="preserve">311
+</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">607
+</t>
+        </is>
+      </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>146</t>
+          <t xml:space="preserve">860
+</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4590
+          <t xml:space="preserve">9590
 </t>
         </is>
       </c>
@@ -1274,38 +1559,64 @@
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11140
+          <t xml:space="preserve">11940
 </t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="S9" s="3" t="n"/>
-      <c r="T9" s="3" t="n"/>
-      <c r="U9" s="3" t="n"/>
+          <t xml:space="preserve">881
+</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">068
+</t>
+        </is>
+      </c>
+      <c r="T9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21626
+</t>
+        </is>
+      </c>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">220
+</t>
+        </is>
+      </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
-        </is>
-      </c>
-      <c r="W9" s="3" t="n"/>
+          <t xml:space="preserve">9590
+</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0098
+</t>
+        </is>
+      </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">897
 </t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
-</t>
-        </is>
-      </c>
-      <c r="Z9" s="3" t="n"/>
+          <t xml:space="preserve">4198
+</t>
+        </is>
+      </c>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1319,65 +1630,142 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C10" s="3" t="n"/>
-      <c r="D10" s="3" t="n"/>
-      <c r="E10" s="3" t="n"/>
-      <c r="F10" s="3" t="n"/>
-      <c r="G10" s="3" t="n"/>
-      <c r="H10" s="3" t="n"/>
-      <c r="I10" s="3" t="n"/>
-      <c r="J10" s="3" t="n"/>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4490
+</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">237
+</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">135
+</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">33
+</t>
+        </is>
+      </c>
       <c r="K10" s="3" t="n"/>
-      <c r="L10" s="3" t="n"/>
-      <c r="M10" s="3" t="n"/>
-      <c r="N10" s="3" t="n"/>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">147
+</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4590
-</t>
-        </is>
-      </c>
-      <c r="P10" s="3" t="n"/>
-      <c r="Q10" s="3" t="n"/>
+          <t xml:space="preserve">918
+</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">858
+</t>
+        </is>
+      </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="S10" s="3" t="n"/>
-      <c r="T10" s="3" t="n"/>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="T10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">629
+</t>
+        </is>
+      </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t xml:space="preserve">106
+</t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8908
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">897
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4150
+          <t xml:space="preserve">830
 </t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -1396,87 +1784,112 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94450
+          <t xml:space="preserve">2218
 </t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="n"/>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="n"/>
+          <t xml:space="preserve">07
+</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1108
+</t>
+        </is>
+      </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
-        </is>
-      </c>
-      <c r="O11" s="3" t="n"/>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">880
+</t>
+        </is>
+      </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="Q11" s="3" t="n"/>
+          <t xml:space="preserve">2104
+</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
-      <c r="T11" s="3" t="n"/>
+          <t xml:space="preserve">1190
+</t>
+        </is>
+      </c>
+      <c r="T11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">284
+</t>
+        </is>
+      </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">106
@@ -1485,7 +1898,7 @@
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -1523,96 +1936,148 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2918
-</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="n"/>
+          <t xml:space="preserve">2290
+</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">224
+</t>
+        </is>
+      </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="n"/>
+          <t xml:space="preserve">133
+</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="n"/>
+          <t xml:space="preserve">1130
+</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="n"/>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="N12" s="3" t="n"/>
-      <c r="O12" s="3" t="n"/>
+          <t xml:space="preserve">1835
+</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">120
+</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">928
+</t>
+        </is>
+      </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">12
+</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1884
+          <t xml:space="preserve">745
 </t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="W12" s="3" t="n"/>
-      <c r="X12" s="3" t="n"/>
-      <c r="Y12" s="3" t="n"/>
-      <c r="Z12" s="3" t="n"/>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2408
+</t>
+        </is>
+      </c>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38
+</t>
+        </is>
+      </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
           <t>7</t>
@@ -1626,61 +2091,109 @@
           <t>8</t>
         </is>
       </c>
-      <c r="C13" s="3" t="n"/>
-      <c r="D13" s="3" t="n"/>
-      <c r="E13" s="3" t="n"/>
-      <c r="F13" s="3" t="n"/>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3220
+</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">236
+</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1188
+</t>
+        </is>
+      </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>281</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="n"/>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">157
+</t>
+        </is>
+      </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">150
+</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">945
+</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1158
+</t>
+        </is>
+      </c>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">148
 </t>
         </is>
       </c>
-      <c r="M13" s="3" t="n"/>
-      <c r="N13" s="3" t="n"/>
-      <c r="O13" s="3" t="n"/>
-      <c r="P13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="Q13" s="3" t="n"/>
-      <c r="R13" s="3" t="n"/>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">905
 </t>
         </is>
       </c>
@@ -1692,29 +2205,34 @@
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
-        </is>
-      </c>
-      <c r="Z13" s="3" t="n"/>
+          <t xml:space="preserve">800
+</t>
+        </is>
+      </c>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
           <t>8</t>
@@ -1728,15 +2246,45 @@
           <t>9</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n"/>
-      <c r="D14" s="3" t="n"/>
-      <c r="E14" s="3" t="n"/>
-      <c r="F14" s="3" t="n"/>
-      <c r="G14" s="3" t="n"/>
-      <c r="H14" s="3" t="n"/>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3240
+</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">236
+</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">134
+</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">84
+</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">125
+</t>
+        </is>
+      </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">1214
 </t>
         </is>
       </c>
@@ -1746,49 +2294,99 @@
 </t>
         </is>
       </c>
-      <c r="K14" s="3" t="n"/>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
-        </is>
-      </c>
-      <c r="M14" s="3" t="n"/>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">137
+</t>
+        </is>
+      </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
-        </is>
-      </c>
-      <c r="O14" s="3" t="n"/>
-      <c r="P14" s="3" t="n"/>
-      <c r="Q14" s="3" t="n"/>
-      <c r="R14" s="3" t="n"/>
-      <c r="S14" s="3" t="n"/>
+          <t xml:space="preserve">154
+</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">940
+</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">213
+</t>
+        </is>
+      </c>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
-      <c r="U14" s="3" t="n"/>
-      <c r="V14" s="3" t="n"/>
+          <t xml:space="preserve">719
+</t>
+        </is>
+      </c>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">72
+</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
-</t>
-        </is>
-      </c>
-      <c r="X14" s="3" t="n"/>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
+          <t xml:space="preserve">875
 </t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -1805,67 +2403,140 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C15" s="3" t="n"/>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3079
+</t>
+        </is>
+      </c>
       <c r="D15" s="3" t="n"/>
-      <c r="E15" s="3" t="n"/>
-      <c r="F15" s="3" t="n"/>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">132
+</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>783</t>
+        </is>
+      </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="n"/>
-      <c r="I15" s="3" t="n"/>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="n"/>
-      <c r="L15" s="3" t="n"/>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">59
+</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
+          <t>1481</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="O15" s="3" t="n"/>
+          <t xml:space="preserve">155
+</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">968
+</t>
+        </is>
+      </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
-        </is>
-      </c>
-      <c r="Q15" s="3" t="n"/>
-      <c r="R15" s="3" t="n"/>
-      <c r="S15" s="3" t="n"/>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165
+</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">719
-</t>
-        </is>
-      </c>
-      <c r="U15" s="3" t="n"/>
-      <c r="V15" s="3" t="n"/>
+          <t xml:space="preserve">730
+</t>
+        </is>
+      </c>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">62
+</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="X15" s="3" t="n"/>
-      <c r="Y15" s="3" t="n"/>
+          <t xml:space="preserve">157
+</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="Y15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">920
+</t>
+        </is>
+      </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -1882,75 +2553,148 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C16" s="3" t="n"/>
-      <c r="D16" s="3" t="n"/>
-      <c r="E16" s="3" t="n"/>
-      <c r="F16" s="3" t="n"/>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19722
+</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1148
+</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">911
+</t>
+        </is>
+      </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="n"/>
-      <c r="I16" s="3" t="n"/>
-      <c r="J16" s="3" t="n"/>
+          <t xml:space="preserve">474
+</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6494
+</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">59
+</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">69
+</t>
+        </is>
+      </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
-</t>
-        </is>
-      </c>
-      <c r="L16" s="3" t="n"/>
-      <c r="M16" s="3" t="n"/>
+          <t xml:space="preserve">468
+</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1912
+</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">694
+</t>
+        </is>
+      </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>11642</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">648
+</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60
+</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">969
 </t>
         </is>
       </c>
-      <c r="P16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="Q16" s="3" t="n"/>
-      <c r="R16" s="3" t="n"/>
-      <c r="S16" s="3" t="n"/>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">838
+</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">884
+</t>
+        </is>
+      </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">730
-</t>
-        </is>
-      </c>
-      <c r="U16" s="3" t="n"/>
+          <t xml:space="preserve">1648
+</t>
+        </is>
+      </c>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248
+</t>
+        </is>
+      </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">845
 </t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
-        </is>
-      </c>
-      <c r="X16" s="3" t="n"/>
+          <t xml:space="preserve">1806
+</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">851
+</t>
+        </is>
+      </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
-        </is>
-      </c>
-      <c r="Z16" s="3" t="n"/>
+          <t xml:space="preserve">4888
+</t>
+        </is>
+      </c>
+      <c r="Z16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1966,48 +2710,49 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19722
+          <t xml:space="preserve">2250
 </t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11148
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1674
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
+          <t xml:space="preserve">1418
 </t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1474
+          <t xml:space="preserve">95
 </t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">129
+</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>691</t>
+          <t xml:space="preserve">4214
+</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
@@ -2018,81 +2763,91 @@
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>196</t>
+          <t xml:space="preserve">146
+</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1694
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>1164646</t>
-        </is>
-      </c>
-      <c r="O17" s="3" t="n"/>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">929
+</t>
+        </is>
+      </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>60</t>
+          <t xml:space="preserve">12
+</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0962
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0828
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8880
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t>3245</t>
+          <t xml:space="preserve">189
+</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t>84</t>
+          <t xml:space="preserve">169
+</t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17186
+          <t xml:space="preserve">157
 </t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">861
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24208
+          <t xml:space="preserve">901
 </t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -2111,76 +2866,118 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2250
+          <t xml:space="preserve">4288
 </t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1239
-</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="n"/>
-      <c r="F18" s="3" t="n"/>
-      <c r="G18" s="3" t="n"/>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
-</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="n"/>
+          <t xml:space="preserve">36
+</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>346</t>
+          <t xml:space="preserve">140
+</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
-        </is>
-      </c>
-      <c r="N18" s="3" t="n"/>
+          <t xml:space="preserve">150
+</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="P18" s="3" t="n"/>
-      <c r="Q18" s="3" t="n"/>
+          <t xml:space="preserve">910
+</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t>4161</t>
+          <t xml:space="preserve">181
+</t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">789
-</t>
-        </is>
-      </c>
-      <c r="U18" s="3" t="n"/>
+          <t xml:space="preserve">691
+</t>
+        </is>
+      </c>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">169
@@ -2189,12 +2986,22 @@
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
-        </is>
-      </c>
-      <c r="X18" s="3" t="n"/>
-      <c r="Y18" s="3" t="n"/>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1150
+</t>
+        </is>
+      </c>
+      <c r="Y18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">818
+</t>
+        </is>
+      </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">20
@@ -2216,79 +3023,130 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4285
+          <t xml:space="preserve">8406
 </t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">140
+</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">140
+</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1121
+</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">34
+</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">151
+</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">115
+</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">920
+</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">249
 </t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="n"/>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124
-</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1109
-</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="n"/>
-      <c r="J19" s="3" t="n"/>
-      <c r="K19" s="3" t="n"/>
-      <c r="L19" s="3" t="n"/>
-      <c r="M19" s="3" t="n"/>
-      <c r="N19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">149
-</t>
-        </is>
-      </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">910
-</t>
-        </is>
-      </c>
-      <c r="P19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="Q19" s="3" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="R19" s="3" t="n"/>
-      <c r="S19" s="3" t="n"/>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1691
+          <t xml:space="preserve">540
 </t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">1144
 </t>
         </is>
       </c>
       <c r="V19" s="3" t="n"/>
-      <c r="W19" s="3" t="n"/>
-      <c r="X19" s="3" t="n"/>
+      <c r="W19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1188
+</t>
+        </is>
+      </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">810
@@ -2297,7 +3155,7 @@
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">274
 </t>
         </is>
       </c>
@@ -2316,73 +3174,148 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24406
+          <t xml:space="preserve">1531
 </t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="n"/>
-      <c r="F20" s="3" t="n"/>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1121
-</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="n"/>
-      <c r="J20" s="3" t="n"/>
-      <c r="K20" s="3" t="n"/>
-      <c r="L20" s="3" t="n"/>
-      <c r="M20" s="3" t="n"/>
-      <c r="N20" s="3" t="n"/>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">34
+</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">56
+</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1194
+</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">151
+</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">970
+</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05
+</t>
+        </is>
+      </c>
+      <c r="Q20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="R20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="S20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="T20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">768
+</t>
+        </is>
+      </c>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">57
+</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="W20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="X20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="Y20" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">920
 </t>
         </is>
       </c>
-      <c r="P20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="Q20" s="3" t="n"/>
-      <c r="R20" s="3" t="n"/>
-      <c r="S20" s="3" t="n"/>
-      <c r="T20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">599
-</t>
-        </is>
-      </c>
-      <c r="U20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1149
-</t>
-        </is>
-      </c>
-      <c r="V20" s="3" t="n"/>
-      <c r="W20" s="3" t="n"/>
-      <c r="X20" s="3" t="n"/>
-      <c r="Y20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">818
-</t>
-        </is>
-      </c>
-      <c r="Z20" s="3" t="n"/>
+      <c r="Z20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
           <t>13</t>
@@ -2398,68 +3331,148 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1531
+          <t xml:space="preserve">2617
 </t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="n"/>
-      <c r="F21" s="3" t="n"/>
-      <c r="G21" s="3" t="n"/>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">147
+</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">74
+</t>
+        </is>
+      </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="n"/>
-      <c r="J21" s="3" t="n"/>
+          <t xml:space="preserve">1419
+</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2119
+</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
-</t>
-        </is>
-      </c>
-      <c r="L21" s="3" t="n"/>
-      <c r="M21" s="3" t="n"/>
-      <c r="N21" s="3" t="n"/>
+          <t xml:space="preserve">109
+</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">164
+</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">152
+</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1970
-</t>
-        </is>
-      </c>
-      <c r="P21" s="3" t="n"/>
-      <c r="Q21" s="3" t="n"/>
-      <c r="R21" s="3" t="n"/>
-      <c r="S21" s="3" t="n"/>
+          <t xml:space="preserve">908
+</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1215
+</t>
+        </is>
+      </c>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="S21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">768
-</t>
-        </is>
-      </c>
-      <c r="U21" s="3" t="n"/>
+          <t xml:space="preserve">740
+</t>
+        </is>
+      </c>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6 8
+</t>
+        </is>
+      </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
-</t>
-        </is>
-      </c>
-      <c r="W21" s="3" t="n"/>
-      <c r="X21" s="3" t="n"/>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="W21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1920
-</t>
-        </is>
-      </c>
-      <c r="Z21" s="3" t="n"/>
+          <t xml:space="preserve">8809
+</t>
+        </is>
+      </c>
+      <c r="Z21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
           <t>14</t>
@@ -2475,85 +3488,145 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12617
+          <t xml:space="preserve">1233
 </t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="n"/>
-      <c r="F22" s="3" t="n"/>
-      <c r="G22" s="3" t="n"/>
+          <t xml:space="preserve">11206
+</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1944
+</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">65
+</t>
+        </is>
+      </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="n"/>
+          <t xml:space="preserve">4134
+</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">05
 </t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="n"/>
-      <c r="M22" s="3" t="n"/>
-      <c r="N22" s="3" t="n"/>
+          <t xml:space="preserve">30
+</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">105
+</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">146
+</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">908
-</t>
-        </is>
-      </c>
-      <c r="P22" s="3" t="n"/>
+          <t xml:space="preserve">910
+</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
-        </is>
-      </c>
-      <c r="R22" s="3" t="n"/>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1178
+</t>
+        </is>
+      </c>
+      <c r="T22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">740
+</t>
+        </is>
+      </c>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">62
+</t>
+        </is>
+      </c>
+      <c r="V22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
+      <c r="W22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">189
 </t>
         </is>
       </c>
-      <c r="T22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">740
-</t>
-        </is>
-      </c>
-      <c r="U22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="V22" s="3" t="n"/>
-      <c r="W22" s="3" t="n"/>
-      <c r="X22" s="3" t="n"/>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8709
+          <t xml:space="preserve">945
 </t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -2572,100 +3645,144 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1233
+          <t xml:space="preserve">19212
 </t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1206
-</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="n"/>
+          <t xml:space="preserve">111531
+</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">494
+</t>
+        </is>
+      </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="n"/>
+          <t xml:space="preserve">9408
+</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">431
+</t>
+        </is>
+      </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">934
+          <t xml:space="preserve">698
 </t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="J23" s="3" t="n"/>
+          <t xml:space="preserve">808
+</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
-        </is>
-      </c>
-      <c r="L23" s="3" t="n"/>
-      <c r="M23" s="3" t="n"/>
+          <t xml:space="preserve">382
+</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">161
+</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1221
+</t>
+        </is>
+      </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">8164
 </t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
-</t>
+          <t>649</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1204
-</t>
-        </is>
-      </c>
-      <c r="R23" s="3" t="n"/>
+          <t xml:space="preserve">1090
+</t>
+        </is>
+      </c>
+      <c r="R23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">888
+</t>
+        </is>
+      </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
+          <t xml:space="preserve">900
 </t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">740
+          <t xml:space="preserve">3479
 </t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
-      </c>
-      <c r="V23" s="3" t="n"/>
-      <c r="W23" s="3" t="n"/>
-      <c r="X23" s="3" t="n"/>
+          <t xml:space="preserve">406
+</t>
+        </is>
+      </c>
+      <c r="V23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9189
+</t>
+        </is>
+      </c>
+      <c r="W23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">899
+</t>
+        </is>
+      </c>
+      <c r="X23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9118
+</t>
+        </is>
+      </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">949
+          <t xml:space="preserve">484
 </t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">1138
 </t>
         </is>
       </c>
@@ -2684,133 +3801,145 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19832
+          <t xml:space="preserve">2154
 </t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1131
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">694
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">1183
 </t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9437
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>6444</t>
+          <t xml:space="preserve">698
+</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">382
+</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">152
+</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">924
+</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="R24" s="3" t="inlineStr">
+        <is>
+          <t>478</t>
+        </is>
+      </c>
+      <c r="S24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="T24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">695
+</t>
+        </is>
+      </c>
+      <c r="U24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">81
+</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">183
+</t>
+        </is>
+      </c>
+      <c r="W24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="Y24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">871
+</t>
+        </is>
+      </c>
+      <c r="Z24" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">28
 </t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">99
-</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>3321</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">171621
-</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t>831</t>
-        </is>
-      </c>
-      <c r="N24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">804618
-</t>
-        </is>
-      </c>
-      <c r="O24" s="3" t="n"/>
-      <c r="P24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">70
-</t>
-        </is>
-      </c>
-      <c r="Q24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1090
-</t>
-        </is>
-      </c>
-      <c r="R24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">888
-</t>
-        </is>
-      </c>
-      <c r="S24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">900
-</t>
-        </is>
-      </c>
-      <c r="T24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3479
-</t>
-        </is>
-      </c>
-      <c r="U24" s="3" t="inlineStr">
-        <is>
-          <t>4064</t>
-        </is>
-      </c>
-      <c r="V24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">918
-</t>
-        </is>
-      </c>
-      <c r="W24" s="3" t="inlineStr">
-        <is>
-          <t>655</t>
-        </is>
-      </c>
-      <c r="X24" s="3" t="inlineStr">
-        <is>
-          <t>942</t>
-        </is>
-      </c>
-      <c r="Y24" s="3" t="inlineStr">
-        <is>
-          <t>465</t>
-        </is>
-      </c>
-      <c r="Z24" s="3" t="inlineStr">
-        <is>
-          <t>1984</t>
         </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -2828,91 +3957,142 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2354
+          <t xml:space="preserve">4904
 </t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">2126
 </t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1139
-</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="n"/>
+          <t xml:space="preserve">136
+</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">150
+</t>
+        </is>
+      </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">2128
 </t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t xml:space="preserve">16
+</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="n"/>
-      <c r="L25" s="3" t="n"/>
+          <t xml:space="preserve">1181
+</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">69
+</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
-        </is>
-      </c>
-      <c r="N25" s="3" t="n"/>
+          <t xml:space="preserve">18492
+</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">154
+</t>
+        </is>
+      </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
-</t>
-        </is>
-      </c>
-      <c r="P25" s="3" t="n"/>
+          <t xml:space="preserve">9108
+</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1218
+          <t xml:space="preserve">2019
 </t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="T25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">689
+</t>
+        </is>
+      </c>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1129
+</t>
+        </is>
+      </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">181
 </t>
         </is>
       </c>
-      <c r="T25" s="3" t="n"/>
-      <c r="U25" s="3" t="n"/>
-      <c r="V25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
-      <c r="W25" s="3" t="n"/>
-      <c r="X25" s="3" t="n"/>
-      <c r="Y25" s="3" t="n"/>
+      <c r="Y25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">940
+</t>
+        </is>
+      </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">28
@@ -2934,88 +4114,148 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4904
+          <t xml:space="preserve">2878
 </t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="n"/>
+          <t xml:space="preserve">235
+</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="n"/>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">89
+</t>
+        </is>
+      </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">120
+</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 5
+</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">69
+</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1846
+</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">115
+</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">950
+</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08
+</t>
+        </is>
+      </c>
+      <c r="Q26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">287
+</t>
+        </is>
+      </c>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">173
+</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="T26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">730
+</t>
+        </is>
+      </c>
+      <c r="U26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">66
+</t>
+        </is>
+      </c>
+      <c r="V26" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">129
 </t>
         </is>
       </c>
-      <c r="I26" s="3" t="n"/>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="n"/>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">121
-</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="n"/>
-      <c r="N26" s="3" t="n"/>
-      <c r="O26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">910
-</t>
-        </is>
-      </c>
-      <c r="P26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="Q26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">215
-</t>
-        </is>
-      </c>
-      <c r="R26" s="3" t="n"/>
-      <c r="S26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1176
-</t>
-        </is>
-      </c>
-      <c r="T26" s="3" t="n"/>
-      <c r="U26" s="3" t="n"/>
-      <c r="V26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="X26" s="3" t="n"/>
-      <c r="Y26" s="3" t="n"/>
-      <c r="Z26" s="3" t="n"/>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
+      <c r="X26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1180
+</t>
+        </is>
+      </c>
+      <c r="Y26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">885
+</t>
+        </is>
+      </c>
+      <c r="Z26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
           <t>17</t>
@@ -3029,79 +4269,150 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C27" s="3" t="n"/>
-      <c r="D27" s="3" t="n"/>
-      <c r="E27" s="3" t="n"/>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23059
+</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">189
 </t>
         </is>
       </c>
-      <c r="G27" s="3" t="n"/>
-      <c r="H27" s="3" t="n"/>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">91
+</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
-      <c r="J27" s="3" t="n"/>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219
+</t>
+        </is>
+      </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1846
-</t>
-        </is>
-      </c>
-      <c r="M27" s="3" t="n"/>
+          <t xml:space="preserve">1154
+</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">940
+</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1190
+</t>
+        </is>
+      </c>
+      <c r="T27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="U27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">56
+</t>
+        </is>
+      </c>
+      <c r="V27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="Y27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">910
+</t>
+        </is>
+      </c>
+      <c r="Z27" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">20
 </t>
         </is>
       </c>
-      <c r="O27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">950
-</t>
-        </is>
-      </c>
-      <c r="P27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
-      </c>
-      <c r="Q27" s="3" t="n"/>
-      <c r="R27" s="3" t="n"/>
-      <c r="S27" s="3" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="T27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1730
-</t>
-        </is>
-      </c>
-      <c r="U27" s="3" t="n"/>
-      <c r="V27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="W27" s="3" t="n"/>
-      <c r="X27" s="3" t="n"/>
-      <c r="Y27" s="3" t="n"/>
-      <c r="Z27" s="3" t="n"/>
       <c r="AA27" s="3" t="inlineStr">
         <is>
           <t>18</t>
@@ -3115,80 +4426,148 @@
           <t>19</t>
         </is>
       </c>
-      <c r="C28" s="3" t="n"/>
-      <c r="D28" s="3" t="n"/>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20239
+</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219
+</t>
+        </is>
+      </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="n"/>
-      <c r="H28" s="3" t="n"/>
+          <t xml:space="preserve">11179
+</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
-        </is>
-      </c>
-      <c r="L28" s="3" t="n"/>
-      <c r="M28" s="3" t="n"/>
+          <t xml:space="preserve">1654
+</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">147
+</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
+          <t xml:space="preserve">950
 </t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="Q28" s="3" t="n"/>
-      <c r="R28" s="3" t="n"/>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="Q28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">205
+</t>
+        </is>
+      </c>
+      <c r="R28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="U28" s="3" t="n"/>
-      <c r="V28" s="3" t="n"/>
-      <c r="W28" s="3" t="n"/>
-      <c r="X28" s="3" t="n"/>
-      <c r="Y28" s="3" t="n"/>
-      <c r="Z28" s="3" t="n"/>
+          <t xml:space="preserve">728
+</t>
+        </is>
+      </c>
+      <c r="U28" s="3" t="inlineStr">
+        <is>
+          <t>661</t>
+        </is>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">167
+</t>
+        </is>
+      </c>
+      <c r="W28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="X28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="Y28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">838
+</t>
+        </is>
+      </c>
+      <c r="Z28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32
+</t>
+        </is>
+      </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
           <t>19</t>
@@ -3204,27 +4583,37 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3059
+          <t xml:space="preserve">2898
 </t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="n"/>
-      <c r="F29" s="3" t="n"/>
+          <t xml:space="preserve">1219
+</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1828
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
@@ -3234,43 +4623,108 @@
 </t>
         </is>
       </c>
-      <c r="J29" s="3" t="n"/>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
-        </is>
-      </c>
-      <c r="L29" s="3" t="n"/>
-      <c r="M29" s="3" t="n"/>
+          <t xml:space="preserve">87
+</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">165
+</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">950
+</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">18
 </t>
         </is>
       </c>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1950
-</t>
-        </is>
-      </c>
-      <c r="P29" s="3" t="n"/>
-      <c r="Q29" s="3" t="n"/>
-      <c r="R29" s="3" t="n"/>
-      <c r="S29" s="3" t="n"/>
+      <c r="Q29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">217
+</t>
+        </is>
+      </c>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="U29" s="3" t="n"/>
-      <c r="V29" s="3" t="n"/>
-      <c r="W29" s="3" t="n"/>
-      <c r="X29" s="3" t="n"/>
-      <c r="Y29" s="3" t="n"/>
-      <c r="Z29" s="3" t="n"/>
+          <t xml:space="preserve">700
+</t>
+        </is>
+      </c>
+      <c r="U29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">78
+</t>
+        </is>
+      </c>
+      <c r="V29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="W29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">171
+</t>
+        </is>
+      </c>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="Y29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">850
+</t>
+        </is>
+      </c>
+      <c r="Z29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32
+</t>
+        </is>
+      </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
           <t>20</t>
@@ -3286,83 +4740,146 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2898
+          <t xml:space="preserve">16829
 </t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1219
-</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="n"/>
-      <c r="F30" s="3" t="n"/>
-      <c r="G30" s="3" t="n"/>
+          <t xml:space="preserve">11209
+</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">006
+</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">906
+</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">437
+</t>
+        </is>
+      </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">806
+</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">656
+</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">91
+</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>4566</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>718</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200214
+</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="Q30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">205
+</t>
+        </is>
+      </c>
+      <c r="R30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">874
+</t>
+        </is>
+      </c>
+      <c r="S30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">901
+</t>
+        </is>
+      </c>
+      <c r="T30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5619
+</t>
+        </is>
+      </c>
+      <c r="U30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3946
+</t>
+        </is>
+      </c>
+      <c r="V30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">880
+</t>
+        </is>
+      </c>
+      <c r="W30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">811
+</t>
+        </is>
+      </c>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">188
 </t>
         </is>
       </c>
-      <c r="I30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="K30" s="3" t="n"/>
-      <c r="L30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1148
-</t>
-        </is>
-      </c>
-      <c r="M30" s="3" t="n"/>
-      <c r="N30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="O30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">950
-</t>
-        </is>
-      </c>
-      <c r="P30" s="3" t="n"/>
-      <c r="Q30" s="3" t="n"/>
-      <c r="R30" s="3" t="n"/>
-      <c r="S30" s="3" t="n"/>
-      <c r="T30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="U30" s="3" t="n"/>
-      <c r="V30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="W30" s="3" t="n"/>
-      <c r="X30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1822009
-</t>
-        </is>
-      </c>
-      <c r="Y30" s="3" t="n"/>
-      <c r="Z30" s="3" t="n"/>
+      <c r="Y30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4418
+</t>
+        </is>
+      </c>
+      <c r="Z30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1122
+</t>
+        </is>
+      </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -3378,125 +4895,145 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16099
+          <t xml:space="preserve">3220
 </t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>360</t>
+          <t xml:space="preserve">137
+</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">906
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t xml:space="preserve">88
+</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">866
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>94</t>
+          <t xml:space="preserve">18
+</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">356
-</t>
-        </is>
-      </c>
-      <c r="L31" s="3" t="n"/>
-      <c r="M31" s="3" t="n"/>
-      <c r="N31" s="3" t="n"/>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">143
+</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>420344</t>
+          <t xml:space="preserve">941
+</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t xml:space="preserve">10
+</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1054
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">901
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3611
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">346
+          <t xml:space="preserve">1163
 </t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1888
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94910
+          <t xml:space="preserve">888
 </t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>9416</t>
         </is>
       </c>
       <c r="AA31" s="3" t="inlineStr">
@@ -3514,97 +5051,148 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3220
-</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="n"/>
+          <t xml:space="preserve">4828
+</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">1119
 </t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">88
 </t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">113
-</t>
-        </is>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="n"/>
-      <c r="L32" s="3" t="n"/>
-      <c r="M32" s="3" t="n"/>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">123
+</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1149
+</t>
+        </is>
+      </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
-      <c r="O32" s="3" t="n"/>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8950
+</t>
+        </is>
+      </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">90
+</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">110
 </t>
         </is>
       </c>
-      <c r="Q32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
-        </is>
-      </c>
-      <c r="S32" s="3" t="n"/>
-      <c r="T32" s="3" t="n"/>
+          <t xml:space="preserve">1198
+</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="T32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9011
+</t>
+        </is>
+      </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2810
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t>114</t>
+          <t xml:space="preserve">149
+</t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
-      <c r="X32" s="3" t="n"/>
-      <c r="Y32" s="3" t="n"/>
-      <c r="Z32" s="3" t="n"/>
+          <t xml:space="preserve">1166
+</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">177
+</t>
+        </is>
+      </c>
+      <c r="Y32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">910
+</t>
+        </is>
+      </c>
+      <c r="Z32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
           <t>21</t>
@@ -3618,96 +5206,145 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="3" t="n"/>
-      <c r="D33" s="3" t="n"/>
-      <c r="E33" s="3" t="n"/>
-      <c r="F33" s="3" t="n"/>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4828
+</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">241
+</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1897
+</t>
+        </is>
+      </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">1117
 </t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">49
+</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">123
+</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">130
+</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">930
+</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">10
 </t>
         </is>
       </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="K33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="L33" s="3" t="n"/>
-      <c r="M33" s="3" t="n"/>
-      <c r="N33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="O33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">830
-</t>
-        </is>
-      </c>
-      <c r="P33" s="3" t="n"/>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1170
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>1581</t>
+          <t xml:space="preserve">168
+</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">319
 </t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="V33" s="3" t="n"/>
-      <c r="W33" s="3" t="n"/>
-      <c r="X33" s="3" t="n"/>
+          <t xml:space="preserve">1144
+</t>
+        </is>
+      </c>
+      <c r="V33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="W33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1834
+</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1406
+</t>
+        </is>
+      </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1950
+          <t xml:space="preserve">718
 </t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
@@ -3724,77 +5361,147 @@
           <t>23</t>
         </is>
       </c>
-      <c r="C34" s="3" t="n"/>
-      <c r="D34" s="3" t="n"/>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4928
+</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1250
+</t>
+        </is>
+      </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1115
+          <t xml:space="preserve">11136
 </t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1886
-</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="n"/>
+          <t xml:space="preserve">1083
+</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">231
+</t>
+        </is>
+      </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">949
-</t>
-        </is>
-      </c>
-      <c r="K34" s="3" t="n"/>
-      <c r="L34" s="3" t="n"/>
-      <c r="M34" s="3" t="n"/>
-      <c r="N34" s="3" t="n"/>
+          <t xml:space="preserve">39
+</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">080
+</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">125
+</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1116
+</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
-</t>
-        </is>
-      </c>
-      <c r="P34" s="3" t="n"/>
-      <c r="Q34" s="3" t="n"/>
-      <c r="R34" s="3" t="n"/>
-      <c r="S34" s="3" t="n"/>
+          <t xml:space="preserve">920
+</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="Q34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">239
+</t>
+        </is>
+      </c>
+      <c r="R34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">177
+</t>
+        </is>
+      </c>
+      <c r="S34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1219
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
-</t>
-        </is>
-      </c>
-      <c r="V34" s="3" t="n"/>
-      <c r="W34" s="3" t="n"/>
-      <c r="X34" s="3" t="n"/>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="V34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="W34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="X34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1167
+</t>
+        </is>
+      </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">710
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">892
 </t>
         </is>
       </c>
@@ -3811,33 +5518,47 @@
           <t>24</t>
         </is>
       </c>
-      <c r="C35" s="3" t="n"/>
-      <c r="D35" s="3" t="n"/>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">740
+</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1115
+          <t xml:space="preserve">1136
 </t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1126
+          <t xml:space="preserve">2894
 </t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1258
-</t>
-        </is>
-      </c>
-      <c r="I35" s="3" t="n"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">40
@@ -3850,33 +5571,92 @@
 </t>
         </is>
       </c>
-      <c r="L35" s="3" t="n"/>
-      <c r="M35" s="3" t="n"/>
-      <c r="N35" s="3" t="n"/>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1135
+</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
-        </is>
-      </c>
-      <c r="P35" s="3" t="n"/>
-      <c r="Q35" s="3" t="n"/>
-      <c r="R35" s="3" t="n"/>
-      <c r="S35" s="3" t="n"/>
+          <t xml:space="preserve">91800
+</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2188
+</t>
+        </is>
+      </c>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="S35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">568
-</t>
-        </is>
-      </c>
-      <c r="U35" s="3" t="n"/>
-      <c r="V35" s="3" t="n"/>
-      <c r="W35" s="3" t="n"/>
-      <c r="X35" s="3" t="n"/>
-      <c r="Y35" s="3" t="n"/>
+          <t xml:space="preserve">6008
+</t>
+        </is>
+      </c>
+      <c r="U35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114248
+</t>
+        </is>
+      </c>
+      <c r="V35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">207
+</t>
+        </is>
+      </c>
+      <c r="W35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">177
+</t>
+        </is>
+      </c>
+      <c r="X35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1185
+</t>
+        </is>
+      </c>
+      <c r="Y35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">755
+</t>
+        </is>
+      </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -3893,12 +5673,27 @@
           <t>25</t>
         </is>
       </c>
-      <c r="C36" s="3" t="n"/>
-      <c r="D36" s="3" t="n"/>
-      <c r="E36" s="3" t="n"/>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4983
+</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">242
+</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">139
+</t>
+        </is>
+      </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
@@ -3908,8 +5703,17 @@
 </t>
         </is>
       </c>
-      <c r="H36" s="3" t="n"/>
-      <c r="I36" s="3" t="n"/>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">40
@@ -3918,44 +5722,94 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L36" s="3" t="n"/>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1086
-</t>
-        </is>
-      </c>
-      <c r="N36" s="3" t="n"/>
-      <c r="O36" s="3" t="n"/>
+          <t xml:space="preserve">156
+</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">910
+</t>
+        </is>
+      </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">16
 </t>
         </is>
       </c>
-      <c r="Q36" s="3" t="n"/>
-      <c r="R36" s="3" t="n"/>
-      <c r="S36" s="3" t="n"/>
+      <c r="Q36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11242
+</t>
+        </is>
+      </c>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="S36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1710
+</t>
+        </is>
+      </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">521
-</t>
-        </is>
-      </c>
-      <c r="U36" s="3" t="n"/>
+          <t xml:space="preserve">5521
+</t>
+        </is>
+      </c>
+      <c r="U36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114248
+</t>
+        </is>
+      </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">184
 </t>
         </is>
       </c>
-      <c r="W36" s="3" t="n"/>
-      <c r="X36" s="3" t="n"/>
-      <c r="Y36" s="3" t="n"/>
+      <c r="W36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">159
+</t>
+        </is>
+      </c>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="Y36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">798
+</t>
+        </is>
+      </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">45
@@ -3977,106 +5831,139 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11828
+          <t xml:space="preserve">1228
 </t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1122
-</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="n"/>
+          <t xml:space="preserve">1242
+</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8258
+</t>
+        </is>
+      </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9286
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="n"/>
+          <t xml:space="preserve">229
+</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">040
+</t>
+        </is>
+      </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="J37" s="3" t="n"/>
-      <c r="K37" s="3" t="n"/>
+          <t xml:space="preserve">1108
+</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1229
+</t>
+        </is>
+      </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t xml:space="preserve">291
+</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="N37" s="3" t="n"/>
+          <t xml:space="preserve">80120
+</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94490
+          <t xml:space="preserve">4490
 </t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
-      <c r="Q37" s="3" t="n"/>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
+      <c r="Q37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1134
+</t>
+        </is>
+      </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">010
 </t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2848
+          <t xml:space="preserve">848
 </t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3124
+          <t xml:space="preserve">3134
 </t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12910
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>504</t>
+          <t xml:space="preserve">809
+</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">852
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9092
+          <t xml:space="preserve">9402
 </t>
         </is>
       </c>
@@ -4105,17 +5992,32 @@
 </t>
         </is>
       </c>
-      <c r="D38" s="3" t="n"/>
-      <c r="E38" s="3" t="n"/>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="G38" s="3" t="n"/>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
@@ -4127,14 +6029,20 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="n"/>
+          <t xml:space="preserve">232
+</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1229
+</t>
+        </is>
+      </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>454</t>
+          <t xml:space="preserve">1151
+</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
@@ -4143,10 +6051,15 @@
 </t>
         </is>
       </c>
-      <c r="N38" s="3" t="n"/>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1521
+</t>
+        </is>
+      </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">898
 </t>
         </is>
       </c>
@@ -4156,16 +6069,36 @@
 </t>
         </is>
       </c>
-      <c r="Q38" s="3" t="n"/>
+      <c r="Q38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">227
+</t>
+        </is>
+      </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="S38" s="3" t="n"/>
-      <c r="T38" s="3" t="n"/>
-      <c r="U38" s="3" t="n"/>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="S38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="T38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">621
+</t>
+        </is>
+      </c>
+      <c r="U38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">182
@@ -4174,12 +6107,28 @@
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t>4641</t>
-        </is>
-      </c>
-      <c r="X38" s="3" t="n"/>
-      <c r="Y38" s="3" t="n"/>
-      <c r="Z38" s="3" t="n"/>
+          <t xml:space="preserve">161
+</t>
+        </is>
+      </c>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">171
+</t>
+        </is>
+      </c>
+      <c r="Y38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2249
+</t>
+        </is>
+      </c>
+      <c r="Z38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 0
+</t>
+        </is>
+      </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -4195,93 +6144,148 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13953
+          <t xml:space="preserve">3950
 </t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">1645
 </t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1920
+</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1118
+</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">123
+</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">92
+</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">52
+</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">85
+</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1115
+</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1521
+</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">910
+</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="Q39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1196
+</t>
+        </is>
+      </c>
+      <c r="R39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="S39" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">120
 </t>
         </is>
       </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1187
-</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1118
-</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1128
-</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="J39" s="3" t="n"/>
-      <c r="K39" s="3" t="n"/>
-      <c r="L39" s="3" t="n"/>
-      <c r="M39" s="3" t="n"/>
-      <c r="N39" s="3" t="n"/>
-      <c r="O39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">910
-</t>
-        </is>
-      </c>
-      <c r="P39" s="3" t="inlineStr">
+      <c r="T39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">528
+</t>
+        </is>
+      </c>
+      <c r="U39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
+      <c r="V39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1710
+</t>
+        </is>
+      </c>
+      <c r="W39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="X39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="Y39" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">118
 </t>
         </is>
       </c>
-      <c r="Q39" s="3" t="n"/>
-      <c r="R39" s="3" t="n"/>
-      <c r="S39" s="3" t="n"/>
-      <c r="T39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5208
-</t>
-        </is>
-      </c>
-      <c r="U39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">140
-</t>
-        </is>
-      </c>
-      <c r="V39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1192
-</t>
-        </is>
-      </c>
-      <c r="W39" s="3" t="n"/>
-      <c r="X39" s="3" t="n"/>
-      <c r="Y39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">718
-</t>
-        </is>
-      </c>
-      <c r="Z39" s="3" t="n"/>
+      <c r="Z39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">164
+</t>
+        </is>
+      </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
           <t>26</t>
@@ -4297,64 +6301,140 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>40344</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="n"/>
-      <c r="E40" s="3" t="n"/>
+          <t xml:space="preserve">29421
+</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2188
+</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">191
 </t>
         </is>
       </c>
-      <c r="G40" s="3" t="n"/>
-      <c r="H40" s="3" t="n"/>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">107
+</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1115
+</t>
+        </is>
+      </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">0016
 </t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="K40" s="3" t="n"/>
-      <c r="L40" s="3" t="n"/>
-      <c r="M40" s="3" t="n"/>
-      <c r="N40" s="3" t="n"/>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1160
+</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1150
+</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
-        </is>
-      </c>
-      <c r="P40" s="3" t="n"/>
-      <c r="Q40" s="3" t="n"/>
-      <c r="R40" s="3" t="n"/>
-      <c r="S40" s="3" t="n"/>
-      <c r="T40" s="3" t="n"/>
+          <t xml:space="preserve">2995
+</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">255
+</t>
+        </is>
+      </c>
+      <c r="Q40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="R40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="S40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="T40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">685
+</t>
+        </is>
+      </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
-</t>
-        </is>
-      </c>
-      <c r="W40" s="3" t="n"/>
-      <c r="X40" s="3" t="n"/>
-      <c r="Y40" s="3" t="n"/>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="W40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
+      <c r="X40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="Y40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">720
+</t>
+        </is>
+      </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
@@ -4373,44 +6453,74 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3401
-</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="n"/>
-      <c r="E41" s="3" t="n"/>
-      <c r="F41" s="3" t="n"/>
-      <c r="G41" s="3" t="n"/>
-      <c r="H41" s="3" t="n"/>
+          <t xml:space="preserve">4084
+</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">237
+</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1125
+</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">131
+</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1111
+</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">1111
 </t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
-        </is>
-      </c>
-      <c r="K41" s="3" t="n"/>
+          <t xml:space="preserve">47
+</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">698
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="N41" s="3" t="n"/>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">889
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
@@ -4420,38 +6530,62 @@
 </t>
         </is>
       </c>
-      <c r="Q41" s="3" t="n"/>
-      <c r="R41" s="3" t="n"/>
-      <c r="S41" s="3" t="n"/>
-      <c r="T41" s="3" t="n"/>
+      <c r="Q41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11239
+</t>
+        </is>
+      </c>
+      <c r="R41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">145
+</t>
+        </is>
+      </c>
+      <c r="S41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="T41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1625
+</t>
+        </is>
+      </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>09</t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="X41" s="3" t="n"/>
+          <t xml:space="preserve">1720
+</t>
+        </is>
+      </c>
+      <c r="X41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">830
 </t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -4470,63 +6604,114 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13370
-</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="n"/>
-      <c r="E42" s="3" t="n"/>
-      <c r="F42" s="3" t="n"/>
+          <t xml:space="preserve">3491
+</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1224
+</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
       <c r="G42" s="3" t="n"/>
-      <c r="H42" s="3" t="n"/>
-      <c r="I42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1137
+</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="n"/>
       <c r="J42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">40
 </t>
         </is>
       </c>
-      <c r="K42" s="3" t="n"/>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">146
+</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">889
+</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="Q42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">434
+</t>
+        </is>
+      </c>
+      <c r="R42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46
+</t>
+        </is>
+      </c>
+      <c r="S42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
+      <c r="T42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14605
+</t>
+        </is>
+      </c>
+      <c r="U42" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">104
 </t>
         </is>
       </c>
-      <c r="M42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">139
-</t>
-        </is>
-      </c>
-      <c r="N42" s="3" t="n"/>
-      <c r="O42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">820
-</t>
-        </is>
-      </c>
-      <c r="P42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="Q42" s="3" t="n"/>
-      <c r="R42" s="3" t="n"/>
-      <c r="S42" s="3" t="n"/>
-      <c r="T42" s="3" t="n"/>
-      <c r="U42" s="3" t="inlineStr">
-        <is>
-          <t>1424</t>
-        </is>
-      </c>
-      <c r="V42" s="3" t="n"/>
+      <c r="V42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">168
@@ -4536,13 +6721,13 @@
       <c r="X42" s="3" t="n"/>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">987
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -4561,85 +6746,136 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16531
-</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="n"/>
+          <t xml:space="preserve">5170
+</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="E43" s="3" t="n"/>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="G43" s="3" t="n"/>
-      <c r="H43" s="3" t="n"/>
-      <c r="I43" s="3" t="n"/>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1101
+</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1114
+</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">197
+</t>
+        </is>
+      </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
-</t>
-        </is>
-      </c>
-      <c r="K43" s="3" t="n"/>
+          <t xml:space="preserve">211
+</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01
+</t>
+        </is>
+      </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
-        </is>
-      </c>
-      <c r="N43" s="3" t="n"/>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
-        </is>
-      </c>
-      <c r="P43" s="3" t="n"/>
-      <c r="Q43" s="3" t="n"/>
+          <t xml:space="preserve">820
+</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">1165
 </t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9593
+          <t xml:space="preserve">520
 </t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
-</t>
-        </is>
-      </c>
-      <c r="V43" s="3" t="n"/>
-      <c r="W43" s="3" t="n"/>
-      <c r="X43" s="3" t="n"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
+      <c r="W43" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">780
+          <t xml:space="preserve">818
 </t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
+          <t xml:space="preserve">37
 </t>
         </is>
       </c>
@@ -4658,17 +6894,22 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228301
+          <t xml:space="preserve">6531
 </t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1917
-</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="n"/>
+          <t xml:space="preserve">234
+</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">180
@@ -4676,8 +6917,18 @@
         </is>
       </c>
       <c r="G44" s="3" t="n"/>
-      <c r="H44" s="3" t="n"/>
-      <c r="I44" s="3" t="n"/>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">50
@@ -4692,7 +6943,7 @@
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
@@ -4709,57 +6960,47 @@
 </t>
         </is>
       </c>
-      <c r="P44" s="3" t="n"/>
-      <c r="Q44" s="3" t="n"/>
+      <c r="P44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="Q44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">1681
 </t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9593
-</t>
-        </is>
-      </c>
-      <c r="U44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1108
-</t>
-        </is>
-      </c>
-      <c r="V44" s="3" t="n"/>
-      <c r="W44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">958
-</t>
-        </is>
-      </c>
-      <c r="X44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">996
-</t>
-        </is>
-      </c>
-      <c r="Y44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">780
-</t>
-        </is>
-      </c>
-      <c r="Z44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">287
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">595
+</t>
+        </is>
+      </c>
+      <c r="U44" s="3" t="n"/>
+      <c r="V44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="W44" s="3" t="n"/>
+      <c r="X44" s="3" t="n"/>
+      <c r="Y44" s="3" t="n"/>
+      <c r="Z44" s="3" t="n"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>31</t>
@@ -4775,68 +7016,118 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228301
+          <t xml:space="preserve">22830
 </t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1917
-</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="n"/>
-      <c r="F45" s="3" t="n"/>
+          <t xml:space="preserve">1985
+</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2191
+</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1102
+</t>
+        </is>
+      </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">620
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">1288
 </t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1262
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
-</t>
-        </is>
-      </c>
-      <c r="L45" s="3" t="n"/>
-      <c r="M45" s="3" t="n"/>
-      <c r="N45" s="3" t="n"/>
+          <t xml:space="preserve">101
+</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">825
+</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">880
+</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">918
+</t>
+        </is>
+      </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2409
-</t>
-        </is>
-      </c>
-      <c r="P45" s="3" t="n"/>
-      <c r="Q45" s="3" t="n"/>
-      <c r="R45" s="3" t="n"/>
+          <t xml:space="preserve">2909
+</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1126
+</t>
+        </is>
+      </c>
+      <c r="Q45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1216
+</t>
+        </is>
+      </c>
+      <c r="R45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1041
+</t>
+        </is>
+      </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">982
-</t>
-        </is>
-      </c>
-      <c r="T45" s="3" t="n"/>
-      <c r="U45" s="3" t="n"/>
+          <t xml:space="preserve">998
+</t>
+        </is>
+      </c>
+      <c r="T45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3810
+</t>
+        </is>
+      </c>
+      <c r="U45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1690
+</t>
+        </is>
+      </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1118
@@ -4845,20 +7136,24 @@
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">958
+          <t xml:space="preserve">2208
 </t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
-</t>
-        </is>
-      </c>
-      <c r="Y45" s="3" t="n"/>
+          <t xml:space="preserve">896
+</t>
+        </is>
+      </c>
+      <c r="Y45" s="3" t="inlineStr">
+        <is>
+          <t>46484</t>
+        </is>
+      </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
@@ -4877,19 +7172,20 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294970
+          <t xml:space="preserve">4980
 </t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1236
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">133
+</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
@@ -4900,44 +7196,70 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">44
+</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46
+</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1138
+</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1389
+</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2541
+</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">228
 </t>
         </is>
       </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>444</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="n"/>
-      <c r="L46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">149
-</t>
-        </is>
-      </c>
-      <c r="M46" s="3" t="n"/>
-      <c r="N46" s="3" t="n"/>
-      <c r="O46" s="3" t="n"/>
-      <c r="P46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="Q46" s="3" t="n"/>
       <c r="R46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">171
@@ -4950,22 +7272,48 @@
 </t>
         </is>
       </c>
-      <c r="T46" s="3" t="n"/>
-      <c r="U46" s="3" t="n"/>
+      <c r="T46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">585
+</t>
+        </is>
+      </c>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1142
+</t>
+        </is>
+      </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t>2126</t>
+          <t xml:space="preserve">186
+</t>
         </is>
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="X46" s="3" t="n"/>
-      <c r="Y46" s="3" t="n"/>
-      <c r="Z46" s="3" t="n"/>
+          <t xml:space="preserve">1159
+</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1166
+</t>
+        </is>
+      </c>
+      <c r="Y46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">878
+</t>
+        </is>
+      </c>
+      <c r="Z46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48
+</t>
+        </is>
+      </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>

--- a/results/05_transient_transcription_output/601/original_transcribed_data.xlsx
+++ b/results/05_transient_transcription_output/601/original_transcribed_data.xlsx
@@ -728,14 +728,13 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5829
+          <t xml:space="preserve">5822
 </t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -764,17 +763,19 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>451</t>
+          <t xml:space="preserve">28
+</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">92
+</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -792,7 +793,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -828,24 +829,20 @@
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1520
-</t>
-        </is>
-      </c>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t xml:space="preserve">520
+</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="n"/>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11207
+          <t xml:space="preserve">10 7 1
 </t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -867,13 +864,13 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2889
+          <t xml:space="preserve">3885
 </t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
+          <t xml:space="preserve">2291
 </t>
         </is>
       </c>
@@ -897,7 +894,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1123
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
@@ -909,14 +906,13 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -927,13 +923,13 @@
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -945,7 +941,7 @@
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -999,7 +995,7 @@
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">755
+          <t xml:space="preserve">75
 </t>
         </is>
       </c>
@@ -1042,7 +1038,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -1078,19 +1074,19 @@
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">1309
 </t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
@@ -1108,7 +1104,7 @@
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
@@ -1144,13 +1140,13 @@
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1181
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
@@ -1162,7 +1158,7 @@
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -1191,15 +1187,10 @@
 </t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">132
-</t>
-        </is>
-      </c>
+      <c r="E7" s="3" t="n"/>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11898
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -1211,25 +1202,25 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">1120
 </t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -1241,26 +1232,25 @@
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1236
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">1521
 </t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5930
+          <t xml:space="preserve">2930
 </t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="Q7" s="3" t="n"/>
@@ -1272,7 +1262,7 @@
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -1284,7 +1274,7 @@
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -1296,7 +1286,7 @@
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
@@ -1308,13 +1298,13 @@
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
+          <t xml:space="preserve">822
 </t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
@@ -1339,7 +1329,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">419
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
@@ -1381,8 +1371,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>64</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -1399,13 +1388,13 @@
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">930
 </t>
         </is>
       </c>
@@ -1429,7 +1418,7 @@
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1181
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -1441,7 +1430,7 @@
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">358
 </t>
         </is>
       </c>
@@ -1487,7 +1476,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">616
+          <t xml:space="preserve">656
 </t>
         </is>
       </c>
@@ -1499,56 +1488,49 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8815
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">651
-</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">105
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">631
+</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="n"/>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
+          <t xml:space="preserve">511
 </t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">734
 </t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">607
+          <t xml:space="preserve">689
 </t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9590
-</t>
+          <t>15901</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
@@ -1559,7 +1541,7 @@
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11940
+          <t xml:space="preserve">1140
 </t>
         </is>
       </c>
@@ -1571,13 +1553,13 @@
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">068
+          <t xml:space="preserve">868
 </t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21626
+          <t xml:space="preserve">2126
 </t>
         </is>
       </c>
@@ -1589,13 +1571,13 @@
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9590
+          <t xml:space="preserve">940
 </t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0098
+          <t xml:space="preserve">808
 </t>
         </is>
       </c>
@@ -1607,7 +1589,7 @@
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4198
+          <t xml:space="preserve">8481
 </t>
         </is>
       </c>
@@ -1632,7 +1614,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4490
+          <t xml:space="preserve">4950
 </t>
         </is>
       </c>
@@ -1650,7 +1632,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">1186
 </t>
         </is>
       </c>
@@ -1668,17 +1650,22 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="n"/>
+          <t xml:space="preserve">38
+</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">147
@@ -1699,19 +1686,19 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
+          <t xml:space="preserve">9218
 </t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">11 3 8
 </t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">858
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
@@ -1723,13 +1710,13 @@
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">1782
 </t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">629
+          <t xml:space="preserve">628
 </t>
         </is>
       </c>
@@ -1784,8 +1771,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2218
-</t>
+          <t>9242</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -1796,97 +1782,96 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1181
+</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07
+</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">181
 </t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">07
-</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1108
-</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">140
-</t>
-        </is>
-      </c>
-      <c r="N11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
-</t>
+          <t>8850</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2104
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
@@ -1960,7 +1945,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">991
 </t>
         </is>
       </c>
@@ -1990,13 +1975,13 @@
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1835
+          <t xml:space="preserve">1385
 </t>
         </is>
       </c>
@@ -2008,7 +1993,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -2050,7 +2035,7 @@
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -2068,7 +2053,7 @@
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2408
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
@@ -2111,18 +2096,19 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>281</t>
+          <t xml:space="preserve">98
+</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
@@ -2146,7 +2132,7 @@
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
@@ -2170,7 +2156,8 @@
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>001</t>
+          <t xml:space="preserve">12
+</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -2187,13 +2174,13 @@
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">905
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
@@ -2217,13 +2204,13 @@
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
@@ -2260,14 +2247,13 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">0134
 </t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -2278,25 +2264,24 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>715</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1214
+          <t xml:space="preserve">1118
 </t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">868
 </t>
         </is>
       </c>
@@ -2314,8 +2299,7 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
@@ -2332,8 +2316,7 @@
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
@@ -2344,13 +2327,13 @@
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">719
+          <t xml:space="preserve">715
 </t>
         </is>
       </c>
@@ -2362,7 +2345,7 @@
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
@@ -2418,12 +2401,12 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>783</t>
+          <t>75</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
@@ -2441,7 +2424,7 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">18 2
 </t>
         </is>
       </c>
@@ -2459,7 +2442,8 @@
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>1481</t>
+          <t xml:space="preserve">138
+</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
@@ -2476,7 +2460,7 @@
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
@@ -2555,7 +2539,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19722
+          <t xml:space="preserve">19732
 </t>
         </is>
       </c>
@@ -2567,30 +2551,30 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>274</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">911
+          <t xml:space="preserve">960
 </t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">474
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6494
+          <t xml:space="preserve">644
 </t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -2602,13 +2586,13 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">468
+          <t xml:space="preserve">460
 </t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1912
+          <t xml:space="preserve">732
 </t>
         </is>
       </c>
@@ -2620,43 +2604,39 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>11642</t>
+          <t>154</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">648
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">969
+          <t xml:space="preserve">069
 </t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">838
-</t>
+          <t>614</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">884
+          <t xml:space="preserve">880
 </t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1648
-</t>
+          <t>39452</t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
@@ -2667,13 +2647,13 @@
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">845
+          <t xml:space="preserve">840
 </t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1806
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -2685,7 +2665,7 @@
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4888
+          <t xml:space="preserve">4288
 </t>
         </is>
       </c>
@@ -2710,8 +2690,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2250
-</t>
+          <t>14694</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -2722,18 +2701,18 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">138
+</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1418
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
+          <t xml:space="preserve">9
 </t>
         </is>
       </c>
@@ -2751,13 +2730,13 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4214
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">468
+          <t xml:space="preserve">460
 </t>
         </is>
       </c>
@@ -2775,31 +2754,31 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">929
+</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">198
 </t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">929
-</t>
-        </is>
-      </c>
-      <c r="P17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="Q17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
@@ -2811,13 +2790,13 @@
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">789
 </t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
@@ -2872,13 +2851,13 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -2890,8 +2869,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
@@ -2902,7 +2880,7 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -2914,85 +2892,84 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">140
+</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">130
+</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">910
+</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
+          <t>645</t>
+        </is>
+      </c>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="T18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">691
+</t>
+        </is>
+      </c>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">80
 </t>
         </is>
       </c>
-      <c r="L18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">140
-</t>
-        </is>
-      </c>
-      <c r="M18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">150
-</t>
-        </is>
-      </c>
-      <c r="N18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">144
-</t>
-        </is>
-      </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">910
-</t>
-        </is>
-      </c>
-      <c r="P18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="Q18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="R18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="S18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="T18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">691
-</t>
-        </is>
-      </c>
-      <c r="U18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
+          <t xml:space="preserve">1170
 </t>
         </is>
       </c>
@@ -3023,13 +3000,14 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8406
+          <t xml:space="preserve">4406
 </t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t xml:space="preserve">220
+</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -3046,20 +3024,19 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1121
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -3088,8 +3065,7 @@
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>464</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
@@ -3106,7 +3082,7 @@
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -3130,20 +3106,24 @@
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1144
-</t>
-        </is>
-      </c>
-      <c r="V19" s="3" t="n"/>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>49</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
+          <t xml:space="preserve">11853
 </t>
         </is>
       </c>
@@ -3155,7 +3135,7 @@
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">1274
 </t>
         </is>
       </c>
@@ -3180,7 +3160,7 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
@@ -3192,13 +3172,13 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
@@ -3210,7 +3190,7 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -3258,44 +3238,43 @@
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">876
+</t>
+        </is>
+      </c>
+      <c r="S20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="T20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">768
+</t>
+        </is>
+      </c>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">176
 </t>
         </is>
       </c>
-      <c r="S20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">185
-</t>
-        </is>
-      </c>
-      <c r="T20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">768
-</t>
-        </is>
-      </c>
-      <c r="U20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">57
-</t>
-        </is>
-      </c>
-      <c r="V20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>755</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
@@ -3349,31 +3328,31 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1419
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2119
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -3385,7 +3364,7 @@
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">1562
 </t>
         </is>
       </c>
@@ -3397,8 +3376,7 @@
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>1213</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
@@ -3415,7 +3393,7 @@
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1215
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
@@ -3427,8 +3405,7 @@
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>0431</t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
@@ -3439,13 +3416,13 @@
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6 8
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">4182
 </t>
         </is>
       </c>
@@ -3494,13 +3471,13 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11206
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1944
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -3512,13 +3489,13 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">61
 </t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4134
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
@@ -3530,7 +3507,7 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -3542,7 +3519,7 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -3554,13 +3531,13 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">1689
 </t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -3590,7 +3567,7 @@
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">740
+          <t xml:space="preserve">7408
 </t>
         </is>
       </c>
@@ -3602,7 +3579,7 @@
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
@@ -3626,7 +3603,7 @@
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -3645,38 +3622,35 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19212
-</t>
+          <t>4774</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111531
+          <t xml:space="preserve">1131
 </t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">494
+          <t xml:space="preserve">894
 </t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9408
+          <t xml:space="preserve">910
 </t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">431
-</t>
+          <t>26540</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">698
-</t>
+          <t>6364</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -3687,7 +3661,7 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
@@ -3699,25 +3673,24 @@
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">1614
 </t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1221
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8164
-</t>
+          <t>316</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
@@ -3734,13 +3707,12 @@
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
-</t>
+          <t>888</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">902
 </t>
         </is>
       </c>
@@ -3758,32 +3730,30 @@
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9189
+          <t xml:space="preserve">9198
 </t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
+          <t xml:space="preserve">839
 </t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9118
-</t>
+          <t>9421</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">484
+          <t xml:space="preserve">1488
 </t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="AA23" s="3" t="inlineStr">
@@ -3831,8 +3801,7 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">698
-</t>
+          <t>6364</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
@@ -3855,8 +3824,7 @@
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>459</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
@@ -3867,7 +3835,7 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -3902,7 +3870,7 @@
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">695
+          <t xml:space="preserve">696
 </t>
         </is>
       </c>
@@ -3920,13 +3888,13 @@
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">1168
 </t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -3957,25 +3925,24 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4904
+          <t xml:space="preserve">1304
 </t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2126
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>46431</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -3987,7 +3954,7 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2128
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
@@ -3999,32 +3966,31 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1181
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">59
 </t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18492
+          <t xml:space="preserve">1342
 </t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
@@ -4041,25 +4007,25 @@
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">1729
 </t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">1176
 </t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">689
+          <t xml:space="preserve">681
 </t>
         </is>
       </c>
@@ -4071,13 +4037,12 @@
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
@@ -4114,7 +4079,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2878
+          <t xml:space="preserve">878
 </t>
         </is>
       </c>
@@ -4144,31 +4109,31 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 5
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">59
 </t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1846
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
@@ -4192,13 +4157,13 @@
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
@@ -4228,32 +4193,30 @@
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AA26" s="3" t="inlineStr">
@@ -4271,7 +4234,7 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23059
+          <t xml:space="preserve">059
 </t>
         </is>
       </c>
@@ -4283,115 +4246,113 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">91
+</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">154
+</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">940
+</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="T27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">710
+</t>
+        </is>
+      </c>
+      <c r="U27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">56
+</t>
+        </is>
+      </c>
+      <c r="V27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">91
-</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">149
-</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">219
-</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">108
-</t>
-        </is>
-      </c>
-      <c r="L27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1154
-</t>
-        </is>
-      </c>
-      <c r="M27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="N27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="O27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">940
-</t>
-        </is>
-      </c>
-      <c r="P27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="Q27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
-      <c r="R27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="S27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1190
-</t>
-        </is>
-      </c>
-      <c r="T27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">110
-</t>
-        </is>
-      </c>
-      <c r="U27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">56
-</t>
-        </is>
-      </c>
-      <c r="V27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="W27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -4428,7 +4389,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20239
+          <t xml:space="preserve">3059
 </t>
         </is>
       </c>
@@ -4446,8 +4407,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11179
-</t>
+          <t>119</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
@@ -4458,31 +4418,31 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1654
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
@@ -4494,7 +4454,7 @@
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
@@ -4505,7 +4465,7 @@
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
@@ -4535,7 +4495,7 @@
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>66</t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
@@ -4589,7 +4549,7 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1219
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
@@ -4601,14 +4561,13 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>845</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
@@ -4619,7 +4578,7 @@
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -4631,25 +4590,25 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">67
 </t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">1149
 </t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">844
 </t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -4661,8 +4620,7 @@
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -4685,7 +4643,7 @@
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">700
+          <t xml:space="preserve">709
 </t>
         </is>
       </c>
@@ -4740,19 +4698,19 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16829
+          <t xml:space="preserve">16899
 </t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11209
+          <t xml:space="preserve">11298
 </t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">006
+          <t xml:space="preserve">606
 </t>
         </is>
       </c>
@@ -4776,7 +4734,7 @@
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">656
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
@@ -4788,7 +4746,8 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>4566</t>
+          <t xml:space="preserve">386
+</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
@@ -4799,36 +4758,36 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>718</t>
+          <t xml:space="preserve">16
+</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200214
+          <t xml:space="preserve">4798
 </t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>1052</t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
+          <t xml:space="preserve">274
 </t>
         </is>
       </c>
@@ -4840,7 +4799,7 @@
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5619
+          <t xml:space="preserve">5618
 </t>
         </is>
       </c>
@@ -4852,31 +4811,31 @@
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="W30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">811
+</t>
+        </is>
+      </c>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">880
 </t>
         </is>
       </c>
-      <c r="W30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">811
-</t>
-        </is>
-      </c>
-      <c r="X30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4418
+          <t xml:space="preserve">4 16 8
 </t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1122
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -4901,7 +4860,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -4925,7 +4884,7 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
@@ -4937,13 +4896,13 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">1 8
 </t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">386
 </t>
         </is>
       </c>
@@ -4955,13 +4914,13 @@
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
@@ -4997,13 +4956,12 @@
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>1163</t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1163
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
@@ -5027,13 +4985,13 @@
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
+          <t xml:space="preserve">883
 </t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t>9416</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AA31" s="3" t="inlineStr">
@@ -5051,7 +5009,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4828
+          <t xml:space="preserve">4818
 </t>
         </is>
       </c>
@@ -5063,19 +5021,19 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1119
+          <t xml:space="preserve">1719
 </t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -5087,61 +5045,60 @@
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
-</t>
+          <t>1051</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8950
+          <t xml:space="preserve">830
 </t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">1158
 </t>
         </is>
       </c>
@@ -5153,7 +5110,7 @@
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9011
+          <t xml:space="preserve">901
 </t>
         </is>
       </c>
@@ -5165,13 +5122,13 @@
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
@@ -5208,43 +5165,43 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4828
+          <t xml:space="preserve">4228
 </t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">2491
 </t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>115</t>
+          <t xml:space="preserve">66184 5
+</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1897
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1117
+          <t xml:space="preserve">1917
 </t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -5255,13 +5212,14 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t xml:space="preserve">161
+</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
@@ -5272,7 +5230,7 @@
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">1924
 </t>
         </is>
       </c>
@@ -5284,7 +5242,7 @@
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
@@ -5302,19 +5260,19 @@
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
+          <t xml:space="preserve">3195
 </t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1144
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
@@ -5326,19 +5284,19 @@
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1834
+          <t xml:space="preserve">1134
 </t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1406
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">718
+          <t xml:space="preserve">710
 </t>
         </is>
       </c>
@@ -5369,19 +5327,18 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1250
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11136
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -5393,25 +5350,24 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1083
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">080
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -5423,13 +5379,13 @@
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1116
+          <t xml:space="preserve">1916
 </t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">811
 </t>
         </is>
       </c>
@@ -5441,7 +5397,7 @@
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -5453,7 +5409,7 @@
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -5465,7 +5421,7 @@
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">568
 </t>
         </is>
       </c>
@@ -5483,16 +5439,11 @@
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="X34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1167
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="X34" s="3" t="n"/>
       <c r="Y34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">210
@@ -5501,7 +5452,7 @@
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">892
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
@@ -5520,13 +5471,13 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">740
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">2180
 </t>
         </is>
       </c>
@@ -5538,8 +5489,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -5567,7 +5517,7 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -5579,72 +5529,73 @@
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1135
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">900
+</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248
+</t>
+        </is>
+      </c>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="S35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="T35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600
+</t>
+        </is>
+      </c>
+      <c r="U35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="V35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">207
+</t>
+        </is>
+      </c>
+      <c r="W35" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">17
 </t>
         </is>
       </c>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">91800
-</t>
-        </is>
-      </c>
-      <c r="P35" s="3" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="Q35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2188
-</t>
-        </is>
-      </c>
-      <c r="R35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="S35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="T35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6008
-</t>
-        </is>
-      </c>
-      <c r="U35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114248
-</t>
-        </is>
-      </c>
-      <c r="V35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">207
-</t>
-        </is>
-      </c>
-      <c r="W35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">177
-</t>
-        </is>
-      </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1185
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -5693,24 +5644,24 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">1921
 </t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1103
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -5740,7 +5691,7 @@
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">1811
 </t>
         </is>
       </c>
@@ -5758,7 +5709,7 @@
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11242
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
@@ -5770,19 +5721,19 @@
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1710
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5521
+          <t xml:space="preserve">551
 </t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114248
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -5831,86 +5782,84 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1228
+          <t xml:space="preserve">1281
 </t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1242
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8258
+          <t xml:space="preserve">698
 </t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">926
 </t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">040
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
+          <t xml:space="preserve">1106
 </t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
+          <t xml:space="preserve">1218
 </t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">831
 </t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80120
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4490
-</t>
+          <t>449303</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>62</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -5921,13 +5870,13 @@
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">010
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -5939,13 +5888,13 @@
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">910
 </t>
         </is>
       </c>
@@ -5957,19 +5906,18 @@
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">832
 </t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9402
-</t>
+          <t>412524</t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1281
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
@@ -5988,7 +5936,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94386
+          <t xml:space="preserve">4386
 </t>
         </is>
       </c>
@@ -6012,36 +5960,36 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>185</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1151
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
@@ -6053,19 +6001,18 @@
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1521
+          <t xml:space="preserve">1581
 </t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">898
-</t>
+          <t>898</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -6083,14 +6030,12 @@
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>4805</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">621
-</t>
+          <t>639</t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
@@ -6107,7 +6052,7 @@
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
@@ -6119,13 +6064,13 @@
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2249
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 0
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -6144,19 +6089,19 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3950
+          <t xml:space="preserve">23923
 </t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1645
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1920
+          <t xml:space="preserve">1230
 </t>
         </is>
       </c>
@@ -6168,19 +6113,19 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
+          <t xml:space="preserve">1119
 </t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -6192,25 +6137,25 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1115
+          <t xml:space="preserve">51
 </t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1521
+          <t xml:space="preserve">5015
 </t>
         </is>
       </c>
@@ -6228,7 +6173,7 @@
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1196
+          <t xml:space="preserve">296
 </t>
         </is>
       </c>
@@ -6240,31 +6185,31 @@
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">528
+          <t xml:space="preserve">520
 </t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1710
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
@@ -6276,13 +6221,13 @@
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">710
 </t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
@@ -6307,116 +6252,110 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2188
+          <t xml:space="preserve">2492
 </t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>49</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1115
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0016
-</t>
-        </is>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">806
+</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="n"/>
       <c r="K40" s="3" t="n"/>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
+          <t xml:space="preserve">1120
 </t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="O40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">910
+</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="Q40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="R40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="S40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="T40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">588
+</t>
+        </is>
+      </c>
+      <c r="U40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">120
+</t>
+        </is>
+      </c>
+      <c r="V40" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">194
 </t>
         </is>
       </c>
-      <c r="O40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2995
-</t>
-        </is>
-      </c>
-      <c r="P40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">255
-</t>
-        </is>
-      </c>
-      <c r="Q40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="R40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="S40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
-      <c r="T40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">685
-</t>
-        </is>
-      </c>
-      <c r="U40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
-      <c r="V40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
@@ -6465,7 +6404,7 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1125
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -6477,7 +6416,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1111
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -6489,7 +6428,7 @@
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1111
+          <t xml:space="preserve">9810
 </t>
         </is>
       </c>
@@ -6513,14 +6452,14 @@
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="N41" s="3" t="n"/>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
@@ -6532,13 +6471,13 @@
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11239
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -6550,24 +6489,25 @@
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1625
+          <t xml:space="preserve">625
 </t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t>09</t>
+          <t xml:space="preserve">10
+</t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1720
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
@@ -6585,7 +6525,7 @@
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -6604,19 +6544,19 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3491
+          <t xml:space="preserve">3401
 </t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1224
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
@@ -6629,11 +6569,16 @@
       <c r="G42" s="3" t="n"/>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1137
-</t>
-        </is>
-      </c>
-      <c r="I42" s="3" t="n"/>
+          <t xml:space="preserve">137
+</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">40
@@ -6648,13 +6593,13 @@
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -6678,13 +6623,13 @@
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">434
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
@@ -6696,7 +6641,7 @@
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14605
+          <t xml:space="preserve">605
 </t>
         </is>
       </c>
@@ -6746,13 +6691,13 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5170
+          <t xml:space="preserve">5370
 </t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>495</t>
         </is>
       </c>
       <c r="E43" s="3" t="n"/>
@@ -6764,32 +6709,31 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1101
+          <t xml:space="preserve">1 18
 </t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1114
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
@@ -6800,18 +6744,19 @@
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">151
+</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
@@ -6829,7 +6774,7 @@
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1165
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -6841,13 +6786,13 @@
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">520
-</t>
+          <t>70</t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">112
+</t>
         </is>
       </c>
       <c r="V43" s="3" t="inlineStr">
@@ -6858,7 +6803,7 @@
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
@@ -6894,7 +6839,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6531
+          <t xml:space="preserve">2231
 </t>
         </is>
       </c>
@@ -6943,8 +6888,7 @@
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>151</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
@@ -6962,7 +6906,7 @@
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -6974,7 +6918,7 @@
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1681
+          <t xml:space="preserve">1671
 </t>
         </is>
       </c>
@@ -6993,7 +6937,7 @@
       <c r="U44" s="3" t="n"/>
       <c r="V44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">2181
 </t>
         </is>
       </c>
@@ -7016,144 +6960,144 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22830
+          <t xml:space="preserve">22820
 </t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1985
+          <t xml:space="preserve">19818
 </t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2191
+          <t xml:space="preserve">297
 </t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1102
+          <t xml:space="preserve">1108
 </t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">620
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1288
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">2862
 </t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">1801
 </t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">825
+          <t xml:space="preserve">899
 </t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">070
 </t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
+          <t xml:space="preserve">313
 </t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2909
+          <t xml:space="preserve">2409
 </t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1126
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1216
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1041
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
+          <t xml:space="preserve">922
 </t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3810
+          <t xml:space="preserve">3310
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1690
+          <t xml:space="preserve">1620
 </t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2208
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">896
-</t>
+          <t>360</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t>46484</t>
+          <t xml:space="preserve">9668
+</t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
@@ -7172,7 +7116,7 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4980
+          <t xml:space="preserve">4970
 </t>
         </is>
       </c>
@@ -7184,7 +7128,7 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
@@ -7218,12 +7162,7 @@
 </t>
         </is>
       </c>
-      <c r="K46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46
-</t>
-        </is>
-      </c>
+      <c r="K46" s="3" t="n"/>
       <c r="L46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">149
@@ -7232,25 +7171,25 @@
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1389
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2541
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -7278,12 +7217,7 @@
 </t>
         </is>
       </c>
-      <c r="U46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1142
-</t>
-        </is>
-      </c>
+      <c r="U46" s="3" t="n"/>
       <c r="V46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">186
@@ -7292,19 +7226,19 @@
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1159
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">878
+          <t xml:space="preserve">778
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/601/original_transcribed_data.xlsx
+++ b/results/05_transient_transcription_output/601/original_transcribed_data.xlsx
@@ -728,13 +728,14 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5822
+          <t xml:space="preserve">585
 </t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>84</t>
+          <t xml:space="preserve">251
+</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -769,19 +770,19 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">47
 </t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
@@ -793,7 +794,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">1295
 </t>
         </is>
       </c>
@@ -829,23 +830,23 @@
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">520
-</t>
-        </is>
-      </c>
-      <c r="U4" s="3" t="n"/>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">151
+</t>
+        </is>
+      </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10 7 1
-</t>
-        </is>
-      </c>
-      <c r="W4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">9187
+</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="n"/>
       <c r="X4" s="3" t="n"/>
       <c r="Y4" s="3" t="n"/>
       <c r="Z4" s="3" t="n"/>
@@ -864,13 +865,13 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3885
+          <t xml:space="preserve">388
 </t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2291
+          <t xml:space="preserve">2939
 </t>
         </is>
       </c>
@@ -894,54 +895,55 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1128
+</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">157
+</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1535
+</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">146
+</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">121
 </t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">135
-</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">146
-</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">999
 </t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -953,13 +955,13 @@
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1167
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -971,7 +973,7 @@
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -995,7 +997,7 @@
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
+          <t xml:space="preserve">755
 </t>
         </is>
       </c>
@@ -1020,7 +1022,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5089
+          <t xml:space="preserve">508
 </t>
         </is>
       </c>
@@ -1032,26 +1034,25 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">2128
 </t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -1068,7 +1069,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -1080,19 +1081,19 @@
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1309
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">451
 </t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -1122,7 +1123,7 @@
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">619
+          <t xml:space="preserve">615
 </t>
         </is>
       </c>
@@ -1146,20 +1147,19 @@
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AA6" s="3" t="inlineStr">
@@ -1187,10 +1187,15 @@
 </t>
         </is>
       </c>
-      <c r="E7" s="3" t="n"/>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">132
+</t>
+        </is>
+      </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -1202,13 +1207,13 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -1220,7 +1225,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
@@ -1238,31 +1243,37 @@
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1521
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2930
+          <t xml:space="preserve">524
 </t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="Q7" s="3" t="n"/>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">225
+</t>
+        </is>
+      </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
@@ -1280,13 +1291,13 @@
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">1166
 </t>
         </is>
       </c>
@@ -1298,13 +1309,13 @@
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
+          <t xml:space="preserve">825
 </t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
@@ -1329,7 +1340,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
@@ -1359,96 +1370,111 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">18
 </t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">151
+</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">141
+</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08
+</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">205
+</t>
+        </is>
+      </c>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">18
 </t>
         </is>
       </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">151
-</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">142
-</t>
-        </is>
-      </c>
-      <c r="N8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">930
-</t>
-        </is>
-      </c>
-      <c r="P8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
-      </c>
-      <c r="Q8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">205
-</t>
-        </is>
-      </c>
-      <c r="R8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">175
-</t>
-        </is>
-      </c>
-      <c r="S8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">760
+          <t xml:space="preserve">640
 </t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">358
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">1114
 </t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1168
+</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">160
 </t>
         </is>
       </c>
-      <c r="X8" s="3" t="n"/>
-      <c r="Y8" s="3" t="n"/>
-      <c r="Z8" s="3" t="n"/>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
           <t>5</t>
@@ -1464,19 +1490,19 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22249
+          <t xml:space="preserve">2224
 </t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1185
+          <t xml:space="preserve">11185
 </t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">656
+          <t xml:space="preserve">676
 </t>
         </is>
       </c>
@@ -1488,7 +1514,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">309
 </t>
         </is>
       </c>
@@ -1498,10 +1524,14 @@
 </t>
         </is>
       </c>
-      <c r="I9" s="3" t="n"/>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>7064</t>
+        </is>
+      </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>2604</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
@@ -1518,19 +1548,20 @@
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">689
+          <t xml:space="preserve">002
 </t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">1664
 </t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>15901</t>
+          <t xml:space="preserve">590
+</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
@@ -1553,7 +1584,7 @@
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">868
+          <t xml:space="preserve">862
 </t>
         </is>
       </c>
@@ -1565,40 +1596,35 @@
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1151
+</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1178
+</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">940
 </t>
         </is>
       </c>
-      <c r="W9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">808
-</t>
-        </is>
-      </c>
-      <c r="X9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">897
-</t>
-        </is>
-      </c>
-      <c r="Y9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8481
-</t>
-        </is>
-      </c>
-      <c r="Z9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
+      <c r="Z9" s="3" t="n"/>
       <c r="AA9" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1614,7 +1640,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4950
+          <t xml:space="preserve">445
 </t>
         </is>
       </c>
@@ -1632,7 +1658,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -1650,22 +1676,17 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">97 9
 </t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">33
+</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="n"/>
       <c r="L10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">147
@@ -1686,19 +1707,19 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9218
+          <t xml:space="preserve">998
 </t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11 3 8
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -1710,13 +1731,13 @@
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1782
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">628
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -1728,7 +1749,7 @@
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">1188
 </t>
         </is>
       </c>
@@ -1746,13 +1767,13 @@
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">830
-</t>
-        </is>
-      </c>
-      <c r="Z10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -1771,12 +1792,12 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>9242</t>
+          <t>1918</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
@@ -1788,25 +1809,24 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1181
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -1818,48 +1838,48 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>8850</t>
+          <t xml:space="preserve">889
+</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>64</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -1871,41 +1891,45 @@
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">1406491
 </t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>551</t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">341
 </t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">6817
 </t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">57175
 </t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
-</t>
-        </is>
-      </c>
-      <c r="Z11" s="3" t="n"/>
+          <t xml:space="preserve">804940
+</t>
+        </is>
+      </c>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38
+</t>
+        </is>
+      </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -1921,7 +1945,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2290
+          <t xml:space="preserve">2295
 </t>
         </is>
       </c>
@@ -1933,7 +1957,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
@@ -1945,7 +1969,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">991
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
@@ -1975,25 +1999,25 @@
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">1143
 </t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1385
+          <t xml:space="preserve">1839
 </t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">9318
 </t>
         </is>
       </c>
@@ -2017,49 +2041,37 @@
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">1177
 </t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">745
-</t>
-        </is>
-      </c>
-      <c r="U12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">248
+</t>
+        </is>
+      </c>
+      <c r="U12" s="3" t="n"/>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="W12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="n"/>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>9405</t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -2108,7 +2120,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -2132,7 +2144,7 @@
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
@@ -2144,73 +2156,73 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">161
+</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">925
+</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1158
+</t>
+        </is>
+      </c>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="T13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">61
+</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">169
 </t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">945
-</t>
-        </is>
-      </c>
-      <c r="P13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="Q13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1158
-</t>
-        </is>
-      </c>
-      <c r="R13" s="3" t="inlineStr">
+      <c r="W13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">148
 </t>
         </is>
       </c>
-      <c r="S13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="T13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">205
-</t>
-        </is>
-      </c>
-      <c r="U13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
-      </c>
-      <c r="V13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">167
-</t>
-        </is>
-      </c>
-      <c r="W13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">850
 </t>
         </is>
       </c>
@@ -2241,19 +2253,20 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0134
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>114</t>
+          <t xml:space="preserve">176
+</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -2264,12 +2277,13 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>715</t>
+          <t xml:space="preserve">125
+</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -2281,7 +2295,7 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">868
+          <t xml:space="preserve">568
 </t>
         </is>
       </c>
@@ -2299,12 +2313,13 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>154</t>
+          <t xml:space="preserve">158
+</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
+          <t xml:space="preserve">001
 </t>
         </is>
       </c>
@@ -2316,7 +2331,8 @@
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t xml:space="preserve">217
+</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
@@ -2327,43 +2343,43 @@
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="T14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">719
+</t>
+        </is>
+      </c>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">18
 </t>
         </is>
       </c>
-      <c r="T14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">715
-</t>
-        </is>
-      </c>
-      <c r="U14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">72
-</t>
-        </is>
-      </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">1158
 </t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">1174
 </t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">875
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
@@ -2392,7 +2408,12 @@
 </t>
         </is>
       </c>
-      <c r="D15" s="3" t="n"/>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248
+</t>
+        </is>
+      </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">132
@@ -2401,7 +2422,8 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>75</t>
+          <t xml:space="preserve">189
+</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -2412,31 +2434,31 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18 2
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
@@ -2454,13 +2476,13 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">968
+          <t xml:space="preserve">0911
 </t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -2490,37 +2512,37 @@
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">74
+</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="W15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">62
 </t>
         </is>
       </c>
-      <c r="V15" s="3" t="inlineStr">
+      <c r="Y15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">166
 </t>
         </is>
       </c>
-      <c r="W15" s="3" t="inlineStr">
+      <c r="Z15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">157
-</t>
-        </is>
-      </c>
-      <c r="X15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
-      <c r="Y15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">920
-</t>
-        </is>
-      </c>
-      <c r="Z15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -2539,7 +2561,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19732
+          <t xml:space="preserve">1475
 </t>
         </is>
       </c>
@@ -2551,42 +2573,41 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>6747</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">960
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">874
 </t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">644
+          <t xml:space="preserve">1644
 </t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>51</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">460
+          <t xml:space="preserve">468
 </t>
         </is>
       </c>
@@ -2598,62 +2619,64 @@
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">694
-</t>
+          <t>6341</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>154</t>
+          <t xml:space="preserve">11404
+</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t xml:space="preserve">145
+</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>60</t>
+          <t xml:space="preserve">60
+</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">069
-</t>
+          <t>965</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>614</t>
+          <t xml:space="preserve">830
+</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
-</t>
+          <t>881</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t>39452</t>
+          <t xml:space="preserve">3945
+</t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
+          <t xml:space="preserve">843
 </t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">786
 </t>
         </is>
       </c>
@@ -2665,13 +2688,13 @@
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4288
+          <t xml:space="preserve">12088
 </t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
@@ -2690,29 +2713,31 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>14694</t>
+          <t xml:space="preserve">2950
+</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t xml:space="preserve">088
+</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
+          <t xml:space="preserve">95
 </t>
         </is>
       </c>
@@ -2730,13 +2755,13 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">28 14
 </t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">460
+          <t xml:space="preserve">2695
 </t>
         </is>
       </c>
@@ -2748,70 +2773,70 @@
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">167
+</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="T17" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">929
 </t>
         </is>
       </c>
-      <c r="P17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="Q17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="R17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">167
-</t>
-        </is>
-      </c>
-      <c r="S17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="T17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">789
-</t>
-        </is>
-      </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">50
 </t>
         </is>
       </c>
-      <c r="V17" s="3" t="inlineStr">
+      <c r="W17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">169
 </t>
         </is>
       </c>
-      <c r="W17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">157
-</t>
-        </is>
-      </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">172
@@ -2820,14 +2845,13 @@
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">901
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="AA17" s="3" t="inlineStr">
@@ -2845,7 +2869,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4288
+          <t xml:space="preserve">4283
 </t>
         </is>
       </c>
@@ -2857,131 +2881,122 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>484</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1109
+</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">36
+</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">140
+</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1130
+</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">910
+</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="n"/>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1178
+</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">181
 </t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">109
-</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">36
-</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">140
-</t>
-        </is>
-      </c>
-      <c r="M18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">130
-</t>
-        </is>
-      </c>
-      <c r="N18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">910
-</t>
-        </is>
-      </c>
-      <c r="P18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="Q18" s="3" t="inlineStr">
-        <is>
-          <t>645</t>
-        </is>
-      </c>
-      <c r="R18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="S18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">691
-</t>
+          <t>691</t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">1160
 </t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1170
+          <t xml:space="preserve">1701
 </t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -3006,7 +3021,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
@@ -3024,7 +3039,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">5140
 </t>
         </is>
       </c>
@@ -3036,7 +3051,8 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t xml:space="preserve">25
+</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -3053,7 +3069,7 @@
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">1151
 </t>
         </is>
       </c>
@@ -3065,7 +3081,8 @@
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>464</t>
+          <t xml:space="preserve">155
+</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
@@ -3076,13 +3093,13 @@
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">2149
 </t>
         </is>
       </c>
@@ -3112,18 +3129,19 @@
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t>49</t>
+          <t xml:space="preserve">1870
+</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11853
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
@@ -3135,7 +3153,7 @@
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1274
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
@@ -3160,25 +3178,25 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">1138
 </t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -3190,13 +3208,12 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
@@ -3208,19 +3225,18 @@
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
-</t>
+          <t>454</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -3232,19 +3248,19 @@
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">876
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
@@ -3262,19 +3278,20 @@
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">1176
 </t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>755</t>
+          <t xml:space="preserve">168
+</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
@@ -3316,7 +3333,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
@@ -3334,13 +3351,13 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
@@ -3364,7 +3381,7 @@
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1562
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
@@ -3376,12 +3393,13 @@
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>1213</t>
+          <t xml:space="preserve">117
+</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">908
+          <t xml:space="preserve">998
 </t>
         </is>
       </c>
@@ -3393,7 +3411,7 @@
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">1215
 </t>
         </is>
       </c>
@@ -3405,7 +3423,8 @@
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t>0431</t>
+          <t xml:space="preserve">189
+</t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
@@ -3422,7 +3441,7 @@
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4182
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -3434,13 +3453,13 @@
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8809
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
@@ -3477,7 +3496,7 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
@@ -3489,13 +3508,13 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">1134
 </t>
         </is>
       </c>
@@ -3507,7 +3526,7 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -3519,25 +3538,25 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1689
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">918
 </t>
         </is>
       </c>
@@ -3561,13 +3580,13 @@
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7408
+          <t xml:space="preserve">740
 </t>
         </is>
       </c>
@@ -3579,7 +3598,7 @@
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
@@ -3597,13 +3616,12 @@
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">945
-</t>
+          <t>9470</t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
@@ -3622,7 +3640,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>4774</t>
+          <t>1772</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -3633,32 +3651,29 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">894
+          <t xml:space="preserve">294
 </t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
+          <t xml:space="preserve">918
 </t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>26540</t>
+          <t xml:space="preserve">943
+</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>6364</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">808
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">612
+</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="n"/>
       <c r="J23" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">99
@@ -3667,35 +3682,35 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">382
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1614
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>304</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">18
+</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">70
 </t>
         </is>
       </c>
@@ -3707,7 +3722,8 @@
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>888</t>
+          <t xml:space="preserve">888
+</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
@@ -3730,30 +3746,30 @@
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9198
+          <t xml:space="preserve">919
 </t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">839
-</t>
+          <t>811</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>9421</t>
+          <t>90</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1488
+          <t xml:space="preserve">9295
 </t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t>138</t>
+          <t xml:space="preserve">138
+</t>
         </is>
       </c>
       <c r="AA23" s="3" t="inlineStr">
@@ -3789,112 +3805,115 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">183
+</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">87
+</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">129
+</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5
+</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">152
+</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10434
+</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2211
+</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="R24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="S24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="T24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">696
+</t>
+        </is>
+      </c>
+      <c r="U24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">81
+</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">1183
 </t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">87
-</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>6364</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">382
-</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>459</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">144
-</t>
-        </is>
-      </c>
-      <c r="N24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="O24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">924
-</t>
-        </is>
-      </c>
-      <c r="P24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="Q24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="R24" s="3" t="inlineStr">
-        <is>
-          <t>478</t>
-        </is>
-      </c>
-      <c r="S24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="T24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">696
-</t>
-        </is>
-      </c>
-      <c r="U24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">81
-</t>
-        </is>
-      </c>
-      <c r="V24" s="3" t="inlineStr">
+      <c r="W24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="X24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
-      <c r="W24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1168
-</t>
-        </is>
-      </c>
-      <c r="X24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -3925,7 +3944,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1304
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
@@ -3937,37 +3956,34 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>46431</t>
+          <t xml:space="preserve">131
+</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">1188
 </t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
@@ -3978,66 +3994,61 @@
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1342
+          <t xml:space="preserve">1842
 </t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t xml:space="preserve">15
+</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9108
-</t>
-        </is>
-      </c>
-      <c r="P25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">915
+</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="n"/>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1729
+          <t xml:space="preserve">1174
 </t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">681
-</t>
+          <t>495</t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t>166</t>
+          <t xml:space="preserve">166
+</t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
@@ -4048,8 +4059,7 @@
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
@@ -4060,7 +4070,7 @@
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -4079,25 +4089,25 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">878
+          <t xml:space="preserve">326
 </t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -4115,7 +4125,7 @@
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -4127,19 +4137,19 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">1846
 </t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -4157,7 +4167,7 @@
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
@@ -4169,7 +4179,7 @@
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">2088
 </t>
         </is>
       </c>
@@ -4205,18 +4215,20 @@
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t xml:space="preserve">885
+</t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t xml:space="preserve">126
+</t>
         </is>
       </c>
       <c r="AA26" s="3" t="inlineStr">
@@ -4234,25 +4246,26 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">059
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">1144
 </t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>141</t>
+          <t xml:space="preserve">18
+</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -4263,60 +4276,56 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="n"/>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1154
+</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">940
+</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">12
 </t>
         </is>
       </c>
-      <c r="K27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">108
-</t>
-        </is>
-      </c>
-      <c r="L27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">154
-</t>
-        </is>
-      </c>
-      <c r="M27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="N27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="O27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">940
-</t>
-        </is>
-      </c>
-      <c r="P27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">2108
 </t>
         </is>
       </c>
@@ -4334,13 +4343,13 @@
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">710
+          <t xml:space="preserve">7170
 </t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -4352,7 +4361,7 @@
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -4389,13 +4398,13 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3059
+          <t xml:space="preserve">305
 </t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
@@ -4407,7 +4416,8 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>119</t>
+          <t xml:space="preserve">179
+</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
@@ -4418,43 +4428,44 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">828
 </t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">1154
 </t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">1142
 </t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">185
+</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
@@ -4471,7 +4482,7 @@
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
@@ -4483,8 +4494,7 @@
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>415</t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
@@ -4495,7 +4505,8 @@
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t>66</t>
+          <t xml:space="preserve">66
+</t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
@@ -4524,7 +4535,7 @@
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
@@ -4561,113 +4572,115 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">81
+</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">87
+</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1149
+</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">950
+</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08
+</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">217
+</t>
+        </is>
+      </c>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="T29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="U29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">78
+</t>
+        </is>
+      </c>
+      <c r="V29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="W29" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">171
 </t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>845</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="K29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">67
-</t>
-        </is>
-      </c>
-      <c r="L29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1149
-</t>
-        </is>
-      </c>
-      <c r="M29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">844
-</t>
-        </is>
-      </c>
-      <c r="N29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">950
-</t>
-        </is>
-      </c>
-      <c r="P29" s="3" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="Q29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">217
-</t>
-        </is>
-      </c>
-      <c r="R29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="S29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="T29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">709
-</t>
-        </is>
-      </c>
-      <c r="U29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">78
-</t>
-        </is>
-      </c>
-      <c r="V29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="W29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">171
-</t>
-        </is>
-      </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">1821
 </t>
         </is>
       </c>
@@ -4698,7 +4711,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16899
+          <t xml:space="preserve">16099
 </t>
         </is>
       </c>
@@ -4708,12 +4721,7 @@
 </t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">606
-</t>
-        </is>
-      </c>
+      <c r="E30" s="3" t="n"/>
       <c r="F30" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">906
@@ -4722,13 +4730,12 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">437
-</t>
+          <t>497</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">806
+          <t xml:space="preserve">866
 </t>
         </is>
       </c>
@@ -4740,7 +4747,7 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
@@ -4750,12 +4757,7 @@
 </t>
         </is>
       </c>
-      <c r="L30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
+      <c r="L30" s="3" t="n"/>
       <c r="M30" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">117
@@ -4764,30 +4766,29 @@
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4798
-</t>
+          <t>05</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
-</t>
+          <t>51</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t>1052</t>
+          <t xml:space="preserve">1052
+</t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">874
 </t>
         </is>
       </c>
@@ -4799,19 +4800,19 @@
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5618
+          <t xml:space="preserve">5610
 </t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3946
+          <t xml:space="preserve">345
 </t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">888
 </t>
         </is>
       </c>
@@ -4823,13 +4824,13 @@
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">882
 </t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4 16 8
+          <t xml:space="preserve">4410
 </t>
         </is>
       </c>
@@ -4860,7 +4861,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
@@ -4884,7 +4885,7 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
@@ -4896,102 +4897,94 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 8
-</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">386
-</t>
-        </is>
-      </c>
-      <c r="L31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">149
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="n"/>
+      <c r="L31" s="3" t="n"/>
       <c r="M31" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">147
+</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5
+</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="Q31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">210
+</t>
+        </is>
+      </c>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="T31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">293
+</t>
+        </is>
+      </c>
+      <c r="U31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">69
+</t>
+        </is>
+      </c>
+      <c r="V31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="W31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
+      <c r="X31" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">14
 </t>
         </is>
       </c>
-      <c r="N31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">161
-</t>
-        </is>
-      </c>
-      <c r="O31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">941
-</t>
-        </is>
-      </c>
-      <c r="P31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
-      <c r="Q31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="R31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">175
-</t>
-        </is>
-      </c>
-      <c r="S31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="T31" s="3" t="inlineStr">
-        <is>
-          <t>1163</t>
-        </is>
-      </c>
-      <c r="U31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
-      </c>
-      <c r="V31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="W31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
-      <c r="X31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">177
-</t>
-        </is>
-      </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">883
+          <t xml:space="preserve">1192
 </t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">2144
+</t>
         </is>
       </c>
       <c r="AA31" s="3" t="inlineStr">
@@ -5009,61 +5002,55 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4818
-</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">235
+</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="n"/>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1719
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -5074,7 +5061,7 @@
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">1128
 </t>
         </is>
       </c>
@@ -5098,55 +5085,55 @@
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="T32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">900
+</t>
+        </is>
+      </c>
+      <c r="U32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="V32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">159
+</t>
+        </is>
+      </c>
+      <c r="W32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">156
+</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">188
 </t>
         </is>
       </c>
-      <c r="T32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">901
-</t>
-        </is>
-      </c>
-      <c r="U32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="V32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="W32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">156
-</t>
-        </is>
-      </c>
-      <c r="X32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">177
-</t>
-        </is>
-      </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
@@ -5165,43 +5152,44 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4228
+          <t xml:space="preserve">14828
 </t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2491
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66184 5
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1917
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">1826
 </t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>46</t>
+          <t xml:space="preserve">26
+</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -5212,13 +5200,13 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">865
 </t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
@@ -5230,7 +5218,7 @@
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1924
+          <t xml:space="preserve">1848
 </t>
         </is>
       </c>
@@ -5242,7 +5230,7 @@
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
@@ -5266,7 +5254,7 @@
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3195
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
@@ -5278,19 +5266,19 @@
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">1160
 </t>
         </is>
       </c>
@@ -5321,48 +5309,49 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4928
+          <t xml:space="preserve">4828
 </t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">1441
 </t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>115</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">1126
 </t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">11095
 </t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t xml:space="preserve">39
+</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
@@ -5379,13 +5368,13 @@
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1916
+          <t xml:space="preserve">1116
 </t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
@@ -5409,7 +5398,7 @@
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
@@ -5439,23 +5428,23 @@
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="X34" s="3" t="n"/>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="X34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">210
 </t>
         </is>
       </c>
-      <c r="Z34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42
-</t>
-        </is>
-      </c>
+      <c r="Z34" s="3" t="n"/>
       <c r="AA34" s="3" t="inlineStr">
         <is>
           <t>23</t>
@@ -5471,13 +5460,13 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">94928
 </t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2180
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
@@ -5489,24 +5478,24 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">19
+</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2894
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>72793</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>446</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
@@ -5529,19 +5518,19 @@
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">9100
 </t>
         </is>
       </c>
@@ -5553,7 +5542,7 @@
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">2945
 </t>
         </is>
       </c>
@@ -5571,13 +5560,13 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">600
+          <t xml:space="preserve">6008
 </t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
@@ -5589,19 +5578,19 @@
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">1828
 </t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">755
+          <t xml:space="preserve">1255
 </t>
         </is>
       </c>
@@ -5626,42 +5615,43 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4983
+          <t xml:space="preserve">94989
 </t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">2942
 </t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">1139
 </t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1921
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">14103
 </t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">127
+</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -5679,7 +5669,7 @@
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">1866
 </t>
         </is>
       </c>
@@ -5691,7 +5681,7 @@
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1811
+          <t xml:space="preserve">1174
 </t>
         </is>
       </c>
@@ -5709,7 +5699,7 @@
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">1881
 </t>
         </is>
       </c>
@@ -5721,19 +5711,19 @@
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">551
+          <t xml:space="preserve">521
 </t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
@@ -5751,7 +5741,7 @@
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">1666
 </t>
         </is>
       </c>
@@ -5763,7 +5753,7 @@
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
@@ -5782,84 +5772,78 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1281
+          <t xml:space="preserve">21928
 </t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1191
+</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>6657</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">533
+</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="n"/>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1106
+</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">121
 </t>
         </is>
       </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">698
-</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">926
-</t>
-        </is>
-      </c>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">220
-</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="I37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1106
-</t>
-        </is>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="K37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1218
-</t>
-        </is>
-      </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">831
+          <t xml:space="preserve">757
 </t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">7112
 </t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">716
 </t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>449303</t>
+          <t>44203</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>62</t>
+          <t xml:space="preserve">88
+</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -5876,7 +5860,7 @@
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">848
 </t>
         </is>
       </c>
@@ -5888,7 +5872,7 @@
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">2348
 </t>
         </is>
       </c>
@@ -5900,25 +5884,25 @@
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">809
+          <t xml:space="preserve">804
 </t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">832
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t>412524</t>
+          <t xml:space="preserve">4098
+</t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
-</t>
+          <t>884</t>
         </is>
       </c>
       <c r="AA37" s="3" t="inlineStr">
@@ -5936,7 +5920,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4386
+          <t xml:space="preserve">438
 </t>
         </is>
       </c>
@@ -5948,7 +5932,7 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
@@ -5960,18 +5944,19 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>185</t>
+          <t xml:space="preserve">108
+</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
@@ -5981,16 +5966,10 @@
 </t>
         </is>
       </c>
-      <c r="K38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+      <c r="K38" s="3" t="n"/>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
-</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
@@ -6001,13 +5980,14 @@
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1581
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>898</t>
+          <t xml:space="preserve">152
+</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
@@ -6030,12 +6010,14 @@
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t>4805</t>
+          <t xml:space="preserve">170
+</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t>639</t>
+          <t xml:space="preserve">827
+</t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
@@ -6052,7 +6034,7 @@
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
@@ -6064,13 +6046,13 @@
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">819
 </t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">898
 </t>
         </is>
       </c>
@@ -6089,19 +6071,19 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23923
+          <t xml:space="preserve">395953
 </t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
@@ -6113,7 +6095,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1119
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
@@ -6125,55 +6107,49 @@
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">52
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">130
+</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="n"/>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">161
+</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8115
+</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">016
+</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">18
 </t>
         </is>
       </c>
-      <c r="M39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">51
-</t>
-        </is>
-      </c>
-      <c r="N39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5015
-</t>
-        </is>
-      </c>
-      <c r="O39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">910
-</t>
-        </is>
-      </c>
-      <c r="P39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">296
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
@@ -6185,7 +6161,7 @@
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">1209
 </t>
         </is>
       </c>
@@ -6197,38 +6173,30 @@
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
-        </is>
-      </c>
-      <c r="V39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
+          <t>440</t>
+        </is>
+      </c>
+      <c r="V39" s="3" t="n"/>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">0158
 </t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">710
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>641</t>
         </is>
       </c>
       <c r="AA39" s="3" t="inlineStr">
@@ -6246,47 +6214,55 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29421
-</t>
+          <t>5454</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2492
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>49</t>
+          <t xml:space="preserve">191
+</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">806
-</t>
-        </is>
-      </c>
-      <c r="J40" s="3" t="n"/>
-      <c r="K40" s="3" t="n"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">008
+</t>
+        </is>
+      </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">160
@@ -6295,25 +6271,25 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -6331,7 +6307,7 @@
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
@@ -6355,25 +6331,25 @@
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">1160
 </t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">720
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">4084
 </t>
         </is>
       </c>
@@ -6392,49 +6368,49 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4084
+          <t xml:space="preserve">3401
 </t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">1237
 </t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">1108
 </t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9810
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -6452,14 +6428,19 @@
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
-      <c r="N41" s="3" t="n"/>
+          <t xml:space="preserve">156
+</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">889
 </t>
         </is>
       </c>
@@ -6471,31 +6452,31 @@
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">625
+          <t xml:space="preserve">622
 </t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
@@ -6507,25 +6488,25 @@
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
+          <t xml:space="preserve">1138
 </t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
@@ -6544,74 +6525,79 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3401
+          <t xml:space="preserve">3310
 </t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="G42" s="3" t="n"/>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7
+</t>
+        </is>
+      </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">889
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
@@ -6623,13 +6609,13 @@
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
@@ -6653,26 +6639,31 @@
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="X42" s="3" t="n"/>
+          <t xml:space="preserve">121
+</t>
+        </is>
+      </c>
+      <c r="X42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">1101
 </t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">580
 </t>
         </is>
       </c>
@@ -6691,78 +6682,85 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5370
+          <t xml:space="preserve">5571
 </t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>495</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="n"/>
+          <t xml:space="preserve">134
+</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 18
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">1996
 </t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>07</t>
+          <t xml:space="preserve">00
+</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">1354
 </t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -6774,53 +6772,55 @@
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t>70</t>
+          <t xml:space="preserve">1867
+</t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">1194
 </t>
         </is>
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">910
 </t>
         </is>
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">1226
+</t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -6839,112 +6839,148 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2231
+          <t xml:space="preserve">29830
 </t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
+          <t xml:space="preserve">1417
 </t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1911
+</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">105
+</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">620
+</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">152
+</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">262
+</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1836
+</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">126
 </t>
         </is>
       </c>
-      <c r="F44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="G44" s="3" t="n"/>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">50
-</t>
-        </is>
-      </c>
-      <c r="K44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L44" s="3" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="M44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="N44" s="3" t="n"/>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">53409
 </t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1671
+          <t xml:space="preserve">1024
 </t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">975
 </t>
         </is>
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">595
-</t>
-        </is>
-      </c>
-      <c r="U44" s="3" t="n"/>
+          <t xml:space="preserve">3510
+</t>
+        </is>
+      </c>
+      <c r="U44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">690
+</t>
+        </is>
+      </c>
       <c r="V44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2181
-</t>
-        </is>
-      </c>
-      <c r="W44" s="3" t="n"/>
-      <c r="X44" s="3" t="n"/>
-      <c r="Y44" s="3" t="n"/>
-      <c r="Z44" s="3" t="n"/>
+          <t xml:space="preserve">11115
+</t>
+        </is>
+      </c>
+      <c r="W44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">955
+</t>
+        </is>
+      </c>
+      <c r="X44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">996
+</t>
+        </is>
+      </c>
+      <c r="Y44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4668
+</t>
+        </is>
+      </c>
+      <c r="Z44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">281
+</t>
+        </is>
+      </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>31</t>
@@ -6960,144 +6996,144 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22820
+          <t xml:space="preserve">4970
 </t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19818
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">620
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">894
+</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">006
+</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">152
 </t>
         </is>
       </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2862
-</t>
-        </is>
-      </c>
-      <c r="K45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1801
-</t>
-        </is>
-      </c>
-      <c r="L45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">899
-</t>
-        </is>
-      </c>
-      <c r="M45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">070
-</t>
-        </is>
-      </c>
-      <c r="N45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">313
-</t>
-        </is>
-      </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2409
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">9228
 </t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3310
+          <t xml:space="preserve">585
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1620
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">1186
 </t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t>360</t>
+          <t xml:space="preserve">166
+</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9668
+          <t xml:space="preserve">828
 </t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">448
 </t>
         </is>
       </c>
@@ -7122,129 +7158,139 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">14 5 9
 </t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">69
+</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">44
+</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1120
+</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">901
+</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="T46" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">118
 </t>
         </is>
       </c>
-      <c r="I46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">44
-</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="n"/>
-      <c r="L46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">149
-</t>
-        </is>
-      </c>
-      <c r="M46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">138
-</t>
-        </is>
-      </c>
-      <c r="N46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">68
-</t>
-        </is>
-      </c>
-      <c r="O46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="P46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="Q46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="R46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">171
-</t>
-        </is>
-      </c>
-      <c r="S46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
-      <c r="T46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">585
-</t>
-        </is>
-      </c>
-      <c r="U46" s="3" t="n"/>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14 140
+</t>
+        </is>
+      </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">1 17 5
 </t>
         </is>
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">1111511
 </t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">778
+          <t xml:space="preserve">1120
 </t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/601/original_transcribed_data.xlsx
+++ b/results/05_transient_transcription_output/601/original_transcribed_data.xlsx
@@ -728,122 +728,102 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">585
-</t>
+          <t>585</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
-</t>
+          <t>47</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1295
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>520</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9187
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="W4" s="3" t="n"/>
@@ -865,146 +845,122 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">388
-</t>
+          <t>3883</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2939
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1535
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">999
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">520
-</t>
+          <t>615</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">755
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -1022,144 +978,122 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">508
-</t>
+          <t>5089</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2128
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>80</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">451
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">615
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>5129</t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AA6" s="3" t="inlineStr">
@@ -1177,146 +1111,122 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5129
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>77</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>299</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>151</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>403</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">524
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">591
-</t>
+          <t>640</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>760</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">825
-</t>
+          <t>280</t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="AA7" s="3" t="inlineStr">
@@ -1334,145 +1244,122 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2298
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>1185</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>676</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>931</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
-</t>
+          <t>509</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>631</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>7064</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>2604</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>511</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
-</t>
+          <t>734</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
+          <t>602</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>664</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>590</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>1140</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>881</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>862</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">640
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>530</t>
         </is>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1114
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>900</t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AA8" s="3" t="inlineStr">
@@ -1490,141 +1377,124 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2224
-</t>
+          <t>4450</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11185
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">676
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">931
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">631
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>7064</t>
+          <t>9 21</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>2604</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">511
-</t>
+          <t>511</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">734
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">002
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1664
-</t>
+          <t>664</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">590
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1140
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">881
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2126
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1151
-</t>
+          <t>940</t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
-</t>
+          <t>897</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
-</t>
-        </is>
-      </c>
-      <c r="Z9" s="3" t="n"/>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1640,141 +1510,122 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">445
-</t>
+          <t>450</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97 9
-</t>
+          <t>62</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="n"/>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>918</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>830</t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AA10" s="3" t="inlineStr">
@@ -1797,26 +1648,22 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
@@ -1826,44 +1673,37 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">889
-</t>
+          <t>880</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
@@ -1873,26 +1713,22 @@
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1406491
-</t>
+          <t>2124</t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
@@ -1900,36 +1736,11 @@
           <t>551</t>
         </is>
       </c>
-      <c r="V11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">341
-</t>
-        </is>
-      </c>
-      <c r="W11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6817
-</t>
-        </is>
-      </c>
-      <c r="X11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">57175
-</t>
-        </is>
-      </c>
-      <c r="Y11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">804940
-</t>
-        </is>
-      </c>
-      <c r="Z11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">38
-</t>
-        </is>
-      </c>
+      <c r="V11" s="3" t="n"/>
+      <c r="W11" s="3" t="n"/>
+      <c r="X11" s="3" t="n"/>
+      <c r="Y11" s="3" t="n"/>
+      <c r="Z11" s="3" t="n"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -1945,110 +1756,92 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2295
-</t>
+          <t>2295</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1143
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1839
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9318
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>745</t>
         </is>
       </c>
       <c r="U12" s="3" t="n"/>
@@ -2060,8 +1853,7 @@
       <c r="W12" s="3" t="n"/>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
@@ -2071,8 +1863,7 @@
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AA12" s="3" t="inlineStr">
@@ -2090,146 +1881,122 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3220
-</t>
+          <t>3220</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">925
-</t>
+          <t>945</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>745</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
-</t>
+          <t>62</t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
-</t>
+          <t>850</t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AA13" s="3" t="inlineStr">
@@ -2247,146 +2014,122 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3240
-</t>
+          <t>324</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">568
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">001
-</t>
+          <t>949</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">719
-</t>
+          <t>905</t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>920</t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>719</t>
         </is>
       </c>
       <c r="AA14" s="3" t="inlineStr">
@@ -2404,146 +2147,122 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3079
-</t>
+          <t>3079</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
-</t>
+          <t>53</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0911
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">730
-</t>
+          <t>730</t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
+          <t>62</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="AA15" s="3" t="inlineStr">
@@ -2561,14 +2280,12 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1475
-</t>
+          <t>1475</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -2578,20 +2295,17 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>922</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
-</t>
+          <t>474</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1644
-</t>
+          <t>644</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
@@ -2601,20 +2315,17 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">468
-</t>
+          <t>465</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">732
-</t>
+          <t>732</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
@@ -2624,20 +2335,17 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11404
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -2647,8 +2355,7 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
-</t>
+          <t>835</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
@@ -2658,44 +2365,37 @@
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3945
-</t>
+          <t>3945</t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">843
-</t>
+          <t>843</t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">786
-</t>
+          <t>786</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">851
-</t>
+          <t>861</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12088
-</t>
+          <t>1588</t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="AA16" s="3" t="inlineStr">
@@ -2713,140 +2413,117 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2950
-</t>
+          <t>295</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">088
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
-</t>
+          <t>95</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28 14
-</t>
+          <t>12 14</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2695
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">929
-</t>
+          <t>929</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>789</t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
-</t>
+          <t>50</t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>901</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
@@ -2869,26 +2546,22 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4283
-</t>
+          <t>4285</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
@@ -2898,20 +2571,17 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1109
-</t>
+          <t>109</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
@@ -2921,26 +2591,22 @@
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="P18" s="3" t="n"/>
@@ -2951,14 +2617,12 @@
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
@@ -2968,8 +2632,7 @@
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>80</t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
@@ -2979,14 +2642,12 @@
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1701
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
@@ -2996,8 +2657,7 @@
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AA18" s="3" t="inlineStr">
@@ -3015,146 +2675,122 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4406
-</t>
+          <t>406</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1151
-</t>
+          <t>151</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>920</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2149
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">540
-</t>
+          <t>540</t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1870
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>810</t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AA19" s="3" t="inlineStr">
@@ -3172,38 +2808,32 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1531
-</t>
+          <t>1531</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>89</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
@@ -3213,20 +2843,17 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
@@ -3236,80 +2863,67 @@
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>05</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">768
-</t>
+          <t>768</t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>57</t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>920</t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AA20" s="3" t="inlineStr">
@@ -3327,146 +2941,122 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2617
-</t>
+          <t>2517</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>109</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
-</t>
+          <t>908</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1215
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">740
-</t>
+          <t>740</t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AA21" s="3" t="inlineStr">
@@ -3484,134 +3074,112 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1233
-</t>
+          <t>1933</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>62</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>05</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">740
-</t>
+          <t>740</t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
+          <t>62</t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
@@ -3621,8 +3189,7 @@
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AA22" s="3" t="inlineStr">
@@ -3645,39 +3212,33 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1131
-</t>
+          <t>1131</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
-</t>
+          <t>694</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
-</t>
+          <t>925</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">943
-</t>
+          <t>437</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">612
-</t>
+          <t>612</t>
         </is>
       </c>
       <c r="I23" s="3" t="n"/>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
@@ -3687,14 +3248,12 @@
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>762</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>722</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
@@ -3704,50 +3263,42 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">70
-</t>
+          <t>70</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1090
-</t>
+          <t>1090</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
-</t>
+          <t>888</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
-</t>
+          <t>905</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3479
-</t>
+          <t>3479</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">406
-</t>
+          <t>406</t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">919
-</t>
+          <t>913</t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
@@ -3762,14 +3313,12 @@
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9295
-</t>
+          <t>355</t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="AA23" s="3" t="inlineStr">
@@ -3787,146 +3336,122 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2154
-</t>
+          <t>295</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
+          <t>87</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10434
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2211
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">696
-</t>
+          <t>696</t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">871
-</t>
+          <t>871</t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -3944,26 +3469,22 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
+          <t>4004</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -3988,51 +3509,43 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
-</t>
+          <t>59</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>151</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1842
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">915
-</t>
+          <t>915</t>
         </is>
       </c>
       <c r="P25" s="3" t="n"/>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
@@ -4047,14 +3560,12 @@
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
@@ -4064,14 +3575,12 @@
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
-</t>
+          <t>940</t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AA25" s="3" t="inlineStr">
@@ -4089,146 +3598,122 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
-</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
-</t>
+          <t>89</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1846
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">950
-</t>
+          <t>950</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2088
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">730
-</t>
+          <t>730</t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
-</t>
+          <t>885</t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AA26" s="3" t="inlineStr">
@@ -4246,141 +3731,118 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>2888</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
-</t>
+          <t>235</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="I27" s="3" t="n"/>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
-</t>
+          <t>940</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2108
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7170
-</t>
+          <t>770</t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AA27" s="3" t="inlineStr">
@@ -4398,98 +3860,82 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
-</t>
+          <t>3059</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>80</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
+          <t>09</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">950
-</t>
+          <t>950</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
@@ -4499,44 +3945,37 @@
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">728
-</t>
+          <t>728</t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">838
-</t>
+          <t>830</t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AA28" s="3" t="inlineStr">
@@ -4554,146 +3993,122 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2898
-</t>
+          <t>2898</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">950
-</t>
+          <t>950</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>700</t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
-</t>
+          <t>78</t>
         </is>
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1821
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
-</t>
+          <t>850</t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AA29" s="3" t="inlineStr">
@@ -4711,21 +4126,18 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16099
-</t>
+          <t>16099</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11298
-</t>
+          <t>1129</t>
         </is>
       </c>
       <c r="E30" s="3" t="n"/>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">906
-</t>
+          <t>906</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -4735,39 +4147,33 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">866
-</t>
+          <t>666</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">386
-</t>
+          <t>356</t>
         </is>
       </c>
       <c r="L30" s="3" t="n"/>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>717</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
-</t>
+          <t>798</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
@@ -4782,62 +4188,52 @@
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1052
-</t>
+          <t>1052</t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
-</t>
+          <t>874</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">901
-</t>
+          <t>901</t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5610
-</t>
+          <t>3619</t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">345
-</t>
+          <t>346</t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
-</t>
+          <t>888</t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
-</t>
+          <t>811</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
-</t>
+          <t>885</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4410
-</t>
+          <t>4410</t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="AA30" s="3" t="inlineStr">
@@ -4855,136 +4251,114 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3220
-</t>
+          <t>3220</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K31" s="3" t="n"/>
       <c r="L31" s="3" t="n"/>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
-</t>
+          <t>798</t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>941</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2144
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="AA31" s="3" t="inlineStr">
@@ -5002,33 +4376,28 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
-</t>
+          <t>2355</t>
         </is>
       </c>
       <c r="D32" s="3" t="n"/>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>73</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
@@ -5038,20 +4407,17 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>163</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
@@ -5061,80 +4427,67 @@
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
-</t>
+          <t>830</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
-</t>
+          <t>900</t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>156</t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AA32" s="3" t="inlineStr">
@@ -5152,146 +4505,122 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14828
-</t>
+          <t>4828</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>117</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1826
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
-</t>
+          <t>49</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">865
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1848
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
-</t>
+          <t>930</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>515</t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">710
-</t>
+          <t>770</t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AA33" s="3" t="inlineStr">
@@ -5309,14 +4638,12 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4828
-</t>
+          <t>4828</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1441
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -5326,122 +4653,102 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11095
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1116
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>920</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">568
-</t>
+          <t>568</t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>810</t>
         </is>
       </c>
       <c r="Z34" s="3" t="n"/>
@@ -5460,32 +4767,27 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94928
-</t>
+          <t>4928</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1136
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
@@ -5500,104 +4802,87 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9100
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2945
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6008
-</t>
+          <t>600</t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1828
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1255
-</t>
+          <t>755</t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AA35" s="3" t="inlineStr">
@@ -5615,146 +4900,122 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94989
-</t>
+          <t>989</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2942
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1139
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14103
-</t>
+          <t>103</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1866
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>156</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1881
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">521
-</t>
+          <t>551</t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1666
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">798
-</t>
+          <t>798</t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AA36" s="3" t="inlineStr">
@@ -5772,14 +5033,12 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21928
-</t>
+          <t>1928</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
-</t>
+          <t>1191</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -5794,110 +5053,89 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">533
-</t>
+          <t>533</t>
         </is>
       </c>
       <c r="H37" s="3" t="n"/>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">757
-</t>
+          <t>757</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7112
-</t>
-        </is>
-      </c>
-      <c r="N37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">716
-</t>
-        </is>
-      </c>
+          <t>027</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="n"/>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>44203</t>
+          <t>4490</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
-</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
-</t>
+          <t>848</t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2348
-</t>
+          <t>548</t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">804
-</t>
+          <t>804</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>855</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4098
-</t>
+          <t>095</t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
@@ -5920,50 +5158,42 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">438
-</t>
+          <t>4386</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K38" s="3" t="n"/>
@@ -5974,86 +5204,72 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">827
-</t>
+          <t>627</t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">819
-</t>
+          <t>819</t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">898
-</t>
+          <t>898</t>
         </is>
       </c>
       <c r="AA38" s="3" t="inlineStr">
@@ -6071,69 +5287,54 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">395953
-</t>
+          <t>5953</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">130
-</t>
-        </is>
-      </c>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="n"/>
       <c r="J39" s="3" t="n"/>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8115
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">016
-</t>
+          <t>016</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
@@ -6143,32 +5344,27 @@
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1209
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">520
-</t>
+          <t>520</t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
@@ -6179,14 +5375,12 @@
       <c r="V39" s="3" t="n"/>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
@@ -6219,32 +5413,27 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
@@ -6259,98 +5448,82 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">008
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">588
-</t>
+          <t>585</t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>820</t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4084
-</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AA40" s="3" t="inlineStr">
@@ -6368,146 +5541,122 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3401
-</t>
+          <t>4084</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1237
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">889
-</t>
+          <t>889</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">622
-</t>
+          <t>625</t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>104</t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
-</t>
+          <t>820</t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AA41" s="3" t="inlineStr">
@@ -6525,146 +5674,122 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3310
-</t>
+          <t>3401</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
-</t>
+          <t>77</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">605
-</t>
+          <t>605</t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>104</t>
         </is>
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1101
-</t>
+          <t>280</t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AA42" s="3" t="inlineStr">
@@ -6682,146 +5807,122 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5571
-</t>
+          <t>5370</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1996
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1354
-</t>
+          <t>151</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>920</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>156</t>
         </is>
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1867
-</t>
+          <t>580</t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1226
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>5571</t>
         </is>
       </c>
       <c r="AA43" s="3" t="inlineStr">
@@ -6839,146 +5940,118 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29830
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1417
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1911
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">620
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1836
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">53409
-</t>
-        </is>
-      </c>
-      <c r="Q44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Q44" s="3" t="n"/>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1024
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">975
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3510
-</t>
+          <t>595</t>
         </is>
       </c>
       <c r="U44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">690
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="V44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11115
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">955
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="X44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="Y44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4668
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="Z44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="AA44" s="3" t="inlineStr">
@@ -6996,145 +6069,122 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4970
-</t>
+          <t>29830</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>1417</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>971</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
+          <t>620</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>708</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">894
-</t>
+          <t>894</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">006
-</t>
+          <t>830</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>919</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
+          <t>5409</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>106</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9228
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>1024</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>975</t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">585
-</t>
+          <t>3510</t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>690</t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
-</t>
+          <t>1115</t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
+          <t>959</t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>996</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
-</t>
+          <t>4688</t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">448
-</t>
+          <t>287</t>
         </is>
       </c>
       <c r="AA45" s="3" t="inlineStr">
@@ -7152,146 +6202,122 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4970
-</t>
+          <t>4970</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14 5 9
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">901
-</t>
+          <t>901</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>585</t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14 140
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 17 5
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1111511
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>554</t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/601/original_transcribed_data.xlsx
+++ b/results/05_transient_transcription_output/601/original_transcribed_data.xlsx
@@ -728,7 +728,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>5853</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>270</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>239</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>97</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>220</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>173</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
@@ -1111,69 +1111,69 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
+          <t>2296</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>299</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
-          <t>403</t>
-        </is>
-      </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
           <t>08</t>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>190</t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>22249</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -1294,12 +1294,12 @@
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>601</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>1664</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>3126</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>9 21</t>
+          <t>22 95</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>1664</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>625</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>18</t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>1455</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>625</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>102</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>153</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>192</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t>2124</t>
+          <t>226</t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>170</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>920</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
@@ -1853,7 +1853,7 @@
       <c r="W12" s="3" t="n"/>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>175</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>3240</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>715</t>
         </is>
       </c>
       <c r="AA14" s="3" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>960</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>72</t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>1475</t>
+          <t>14752</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>1148</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -2320,7 +2320,7 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>463</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>7124</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>145</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
@@ -2355,7 +2355,7 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>835</t>
+          <t>832</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>242</t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>1588</t>
+          <t>4502</t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
@@ -2413,22 +2413,22 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>2950</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>280</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>186</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>189</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>12 14</t>
+          <t>0 14</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>102</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>021</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>154</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>180</t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
@@ -2675,7 +2675,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>406</t>
+          <t>4406</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>190</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>200</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>199</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>148</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>22</t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>2517</t>
+          <t>2617</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>162</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>220</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
@@ -3129,7 +3129,7 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>161</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>912</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -3232,7 +3232,7 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>613</t>
         </is>
       </c>
       <c r="I23" s="3" t="n"/>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t>905</t>
+          <t>903</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>228</t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>4355</t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>2954</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>129</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>160</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>929</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>157</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
@@ -3638,7 +3638,7 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>35</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>158</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
@@ -3673,7 +3673,7 @@
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>173</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>2888</t>
+          <t>2878</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>170</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>138</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
@@ -4018,7 +4018,7 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>338</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
@@ -4033,7 +4033,7 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
@@ -4048,7 +4048,7 @@
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>212</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
@@ -4063,7 +4063,7 @@
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>217</t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>792</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t>3619</t>
+          <t>3612</t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>878</t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
@@ -4298,12 +4298,12 @@
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>08</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>160</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>181 1</t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>723</t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>104</t>
         </is>
       </c>
       <c r="AA31" s="3" t="inlineStr">
@@ -4427,7 +4427,7 @@
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>112</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>172</t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>222</t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>06</t>
         </is>
       </c>
       <c r="AA32" s="3" t="inlineStr">
@@ -4505,7 +4505,7 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>4828</t>
+          <t>14828</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>266</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>140</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
@@ -4663,7 +4663,7 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>193</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
@@ -4743,7 +4743,7 @@
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>167</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
@@ -4822,12 +4822,12 @@
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>176</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>900</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
@@ -4900,7 +4900,7 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>4989</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -4955,7 +4955,7 @@
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>172</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
@@ -5010,12 +5010,12 @@
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>790</t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AA36" s="3" t="inlineStr">
@@ -5033,7 +5033,7 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>1928</t>
+          <t>21928</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>3134</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>855</t>
+          <t>853</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t>095</t>
+          <t>4092</t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>132</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>106</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>123</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>08</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>152</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
@@ -5315,7 +5315,11 @@
           <t>120</t>
         </is>
       </c>
-      <c r="I39" s="3" t="n"/>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J39" s="3" t="n"/>
       <c r="K39" s="3" t="inlineStr">
         <is>
@@ -5324,12 +5328,12 @@
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>288</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>115</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
@@ -5413,7 +5417,7 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>245</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -5428,7 +5432,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>226</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
@@ -5463,7 +5467,7 @@
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>101</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
@@ -5513,7 +5517,7 @@
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>162</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
@@ -5551,7 +5555,7 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>122</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -5631,7 +5635,7 @@
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>106</t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
@@ -5641,7 +5645,7 @@
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>170</t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
@@ -5684,7 +5688,7 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>141</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
@@ -5724,7 +5728,7 @@
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>226</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
@@ -5779,12 +5783,12 @@
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>182</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>870</t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
@@ -5862,7 +5866,7 @@
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>162</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
@@ -5902,12 +5906,12 @@
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>172</t>
         </is>
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>152</t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
@@ -5940,7 +5944,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>2371</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
@@ -5995,7 +5999,7 @@
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>192</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
@@ -6016,7 +6020,7 @@
       </c>
       <c r="S44" s="3" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>169</t>
         </is>
       </c>
       <c r="T44" s="3" t="inlineStr">
@@ -6079,7 +6083,7 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>7971</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -6124,7 +6128,7 @@
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>919</t>
+          <t>918</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
@@ -6139,7 +6143,7 @@
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>137</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
@@ -6169,7 +6173,7 @@
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>222</t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
@@ -6179,7 +6183,7 @@
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t>4688</t>
+          <t>4668</t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
@@ -6222,7 +6226,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>103</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
@@ -6242,7 +6246,7 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
@@ -6252,7 +6256,7 @@
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>080</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
@@ -6307,12 +6311,12 @@
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t>554</t>
+          <t>114</t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>190</t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/601/original_transcribed_data.xlsx
+++ b/results/05_transient_transcription_output/601/original_transcribed_data.xlsx
@@ -728,7 +728,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>5853</t>
+          <t>585</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>3883</t>
+          <t>388</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>155</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>185</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
@@ -1033,12 +1033,12 @@
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>224</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>17</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>200</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>280</t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>22249</t>
+          <t>2229</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -1294,12 +1294,12 @@
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>681</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>1664</t>
+          <t>164</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>22 95</t>
+          <t>2 25</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>1664</t>
+          <t>164</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>10</t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>1455</t>
+          <t>1450</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -1535,12 +1535,12 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>212</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>02</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>103</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>152</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>20</t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>130</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>940</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>14752</t>
+          <t>1475</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>912</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>7124</t>
+          <t>124</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
@@ -2355,7 +2355,7 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>835</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>248</t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>4502</t>
+          <t>4500</t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>230</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>136</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>202</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>021</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>155</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>80</t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>170</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>207</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>09</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>178</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>54</t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>168</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>155</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
@@ -3129,7 +3129,7 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>165</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>912</t>
+          <t>913</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -3232,13 +3232,13 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>643</t>
         </is>
       </c>
       <c r="I23" s="3" t="n"/>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>93</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>913</t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>922</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>4004</t>
+          <t>400</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>118</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
@@ -3875,69 +3875,69 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>838</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="P28" s="3" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="Q28" s="3" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="R28" s="3" t="inlineStr">
+        <is>
           <t>170</t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>09</t>
-        </is>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t>154</t>
-        </is>
-      </c>
-      <c r="L28" s="3" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="M28" s="3" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="N28" s="3" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="O28" s="3" t="inlineStr">
-        <is>
-          <t>950</t>
-        </is>
-      </c>
-      <c r="P28" s="3" t="inlineStr">
-        <is>
-          <t>08</t>
-        </is>
-      </c>
-      <c r="Q28" s="3" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="R28" s="3" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
           <t>415</t>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t>830</t>
+          <t>838</t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
@@ -4048,7 +4048,7 @@
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>16</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
@@ -4131,7 +4131,7 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="E30" s="3" t="n"/>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t>3612</t>
+          <t>361</t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
@@ -4298,7 +4298,7 @@
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>05</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
@@ -4323,7 +4323,7 @@
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t>181 1</t>
+          <t>181 2</t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AA31" s="3" t="inlineStr">
@@ -4427,7 +4427,7 @@
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>22</t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>00</t>
         </is>
       </c>
       <c r="AA32" s="3" t="inlineStr">
@@ -4505,7 +4505,7 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>14828</t>
+          <t>4828</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>286</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>13</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>133</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>17</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
@@ -4847,7 +4847,7 @@
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>185</t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
@@ -5015,7 +5015,7 @@
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AA36" s="3" t="inlineStr">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t>4092</t>
+          <t>4090</t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
@@ -5178,7 +5178,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>108</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
@@ -5315,11 +5315,7 @@
           <t>120</t>
         </is>
       </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I39" s="3" t="n"/>
       <c r="J39" s="3" t="n"/>
       <c r="K39" s="3" t="inlineStr">
         <is>
@@ -5328,17 +5324,17 @@
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>160</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>016</t>
+          <t>301</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
@@ -5432,7 +5428,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
@@ -5467,7 +5463,7 @@
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
@@ -5517,12 +5513,12 @@
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>163</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t>820</t>
+          <t>720</t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
@@ -5555,7 +5551,7 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -5600,7 +5596,7 @@
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>198</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
@@ -5645,7 +5641,7 @@
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>178</t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
@@ -5728,7 +5724,7 @@
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>133</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
@@ -5788,7 +5784,7 @@
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>880</t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
@@ -5944,7 +5940,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>2371</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
@@ -5999,7 +5995,7 @@
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
@@ -6020,7 +6016,7 @@
       </c>
       <c r="S44" s="3" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>159</t>
         </is>
       </c>
       <c r="T44" s="3" t="inlineStr">
@@ -6073,7 +6069,7 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>29830</t>
+          <t>2980</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -6173,7 +6169,7 @@
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>955</t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
@@ -6246,7 +6242,7 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
@@ -6256,7 +6252,7 @@
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>080</t>
+          <t>084</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
@@ -6311,7 +6307,7 @@
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
@@ -6321,7 +6317,7 @@
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>00</t>
         </is>
       </c>
       <c r="AA46" s="3" t="inlineStr">
